--- a/src/Documentacion/BIS011APPSY-SeguimientoPlanTrabajoDesaHERRIZ-v2.xlsx
+++ b/src/Documentacion/BIS011APPSY-SeguimientoPlanTrabajoDesaHERRIZ-v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgantolin\BiscaytikApp_node-modules-incluido\src\Documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{935813E1-8E55-4825-AF0C-3C4ECC6F2759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8515182E-BAB6-4A59-BD51-5F4497A91540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="242">
   <si>
     <t>HITO</t>
   </si>
@@ -677,18 +677,12 @@
     <t>Falta estimar funcionalidad compartir.</t>
   </si>
   <si>
-    <t>pequeña corrección pendiente de entregar en listados</t>
-  </si>
-  <si>
     <t>Validación contenido? Ejem. Galería ? (reglas)</t>
   </si>
   <si>
     <t>si no hay contenido no aparece posible?  Estimar</t>
   </si>
   <si>
-    <t>Condicionado. Revisar tab galería</t>
-  </si>
-  <si>
     <t>img's SVGs para poder editarlas por css. Iconos "mejor elegidos"</t>
   </si>
   <si>
@@ -756,6 +750,18 @@
   </si>
   <si>
     <t>Condicionado. Consulta canal</t>
+  </si>
+  <si>
+    <t>Finalizado. Rehecho img 100%</t>
+  </si>
+  <si>
+    <t>En listados repetido por estructura sitio</t>
+  </si>
+  <si>
+    <t>Condicionado. Revisar tab galería?</t>
+  </si>
+  <si>
+    <t>En curso. 1ra prueba hecha.Cuando esté todo el portal revisar acad punto</t>
   </si>
 </sst>
 </file>
@@ -1034,7 +1040,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1180,6 +1186,9 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1197,10 +1206,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1608,7 +1613,7 @@
         <v>180</v>
       </c>
       <c r="AD2" s="35" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="AE2" s="35" t="s">
         <v>181</v>
@@ -1876,10 +1881,10 @@
         <v>167</v>
       </c>
       <c r="AB15" s="19" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AD15" s="43" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="16" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -1926,7 +1931,7 @@
         <v>184</v>
       </c>
       <c r="AA17" s="45" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AD17" s="43" t="s">
         <v>166</v>
@@ -2287,7 +2292,7 @@
         <v>208</v>
       </c>
       <c r="AD30" s="44" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="31" spans="1:31" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -2403,7 +2408,7 @@
         <v>186</v>
       </c>
       <c r="AC35" s="19" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AD35" s="46" t="s">
         <v>209</v>
@@ -2412,7 +2417,7 @@
         <v>186</v>
       </c>
       <c r="AF35" s="19" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="36" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -2623,22 +2628,22 @@
       </c>
       <c r="X43" s="41"/>
       <c r="AA43" s="44" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB43" s="54" t="s">
+        <v>224</v>
+      </c>
+      <c r="AC43" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="AB43" s="54" t="s">
-        <v>226</v>
-      </c>
-      <c r="AC43" s="19" t="s">
-        <v>225</v>
-      </c>
       <c r="AD43" s="44" t="s">
+        <v>221</v>
+      </c>
+      <c r="AE43" s="54" t="s">
+        <v>224</v>
+      </c>
+      <c r="AF43" s="19" t="s">
         <v>223</v>
-      </c>
-      <c r="AE43" s="54" t="s">
-        <v>226</v>
-      </c>
-      <c r="AF43" s="19" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="44" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -2671,7 +2676,7 @@
     </row>
     <row r="45" spans="1:32" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="50" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B45" s="16" t="s">
         <v>64</v>
@@ -2698,19 +2703,19 @@
         <v>210</v>
       </c>
       <c r="AB45" s="19" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AC45" s="19" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AD45" s="44" t="s">
         <v>210</v>
       </c>
       <c r="AE45" s="19" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AF45" s="19" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="46" spans="1:32" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
@@ -3083,7 +3088,7 @@
         <v>212</v>
       </c>
       <c r="AC60" s="19" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AD60" s="43" t="s">
         <v>166</v>
@@ -3092,7 +3097,7 @@
         <v>212</v>
       </c>
       <c r="AF60" s="19" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="61" spans="1:32" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -3123,17 +3128,17 @@
       <c r="Y61" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="AA61" s="44" t="s">
-        <v>167</v>
-      </c>
-      <c r="AB61" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="AD61" s="44" t="s">
-        <v>167</v>
-      </c>
-      <c r="AE61" s="19" t="s">
-        <v>213</v>
+      <c r="AA61" s="43" t="s">
+        <v>166</v>
+      </c>
+      <c r="AB61" s="55" t="s">
+        <v>239</v>
+      </c>
+      <c r="AD61" s="43" t="s">
+        <v>166</v>
+      </c>
+      <c r="AE61" s="55" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="62" spans="1:32" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -3183,7 +3188,7 @@
         <v>189</v>
       </c>
       <c r="AD62" s="43" t="s">
-        <v>166</v>
+        <v>238</v>
       </c>
       <c r="AE62" s="19" t="s">
         <v>190</v>
@@ -3265,16 +3270,16 @@
         <v>193</v>
       </c>
       <c r="AA64" s="44" t="s">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="AB64" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AD64" s="44" t="s">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="AE64" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="65" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -3432,7 +3437,7 @@
         <v>145</v>
       </c>
       <c r="X69" s="37" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="Y69" s="19" t="s">
         <v>194</v>
@@ -3441,7 +3446,7 @@
         <v>202</v>
       </c>
       <c r="AA69" s="46" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AB69" s="19" t="s">
         <v>194</v>
@@ -3450,7 +3455,7 @@
         <v>202</v>
       </c>
       <c r="AD69" s="46" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AE69" s="19" t="s">
         <v>194</v>
@@ -3475,10 +3480,10 @@
     </row>
     <row r="71" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A71" s="49" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C71" s="27" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D71" s="34" t="s">
         <v>92</v>
@@ -3517,10 +3522,10 @@
     </row>
     <row r="72" spans="1:32" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A72" s="49" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C72" s="27" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D72" s="13" t="s">
         <v>94</v>
@@ -3560,16 +3565,16 @@
         <v>169</v>
       </c>
       <c r="AB72" s="19" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AC72" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="AD72" s="46" t="s">
-        <v>169</v>
+      <c r="AD72" s="45" t="s">
+        <v>241</v>
       </c>
       <c r="AE72" s="19" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AF72" s="19" t="s">
         <v>197</v>
@@ -3619,13 +3624,13 @@
         <v>169</v>
       </c>
       <c r="AB73" s="19" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AD73" s="46" t="s">
         <v>169</v>
       </c>
       <c r="AE73" s="19" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="74" spans="1:32" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -3660,13 +3665,13 @@
         <v>169</v>
       </c>
       <c r="AB74" s="19" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AD74" s="46" t="s">
         <v>169</v>
       </c>
       <c r="AE74" s="19" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="75" spans="1:32" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -3700,13 +3705,13 @@
         <v>167</v>
       </c>
       <c r="AC75" s="19" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AD75" s="44" t="s">
         <v>167</v>
       </c>
       <c r="AF75" s="19" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="76" spans="1:32" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -3743,13 +3748,13 @@
         <v>169</v>
       </c>
       <c r="AB76" s="19" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AD76" s="46" t="s">
         <v>169</v>
       </c>
       <c r="AE76" s="19" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="77" spans="1:32" ht="63" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -3966,24 +3971,24 @@
         <v>169</v>
       </c>
       <c r="AB81" s="19" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AC81" s="19" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AD81" s="46" t="s">
         <v>169</v>
       </c>
       <c r="AE81" s="19" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AF81" s="19" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="82" spans="1:32" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A82" s="50" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B82" s="16" t="s">
         <v>112</v>
@@ -4177,7 +4182,7 @@
     </row>
     <row r="91" spans="1:32" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A91" s="50" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B91" s="16" t="s">
         <v>125</v>
@@ -4347,38 +4352,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Estado xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">En curso</Estado>
-    <Area xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">7</Area>
-    <Acciones xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
-    <sys xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
-    <Sociedad xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
-    <fechadeproyecto xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">2022-07-13T22:00:00+00:00</fechadeproyecto>
-    <OfertaAnterior xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
-    <DocumentSetDescription xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Oferta xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">
-      <Value>5919</Value>
-    </Oferta>
-    <responsableproyecto xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">
-      <UserInfo>
-        <DisplayName>Aitor Roncero Val</DisplayName>
-        <AccountId>927</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </responsableproyecto>
-    <Oficina xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">1</Oficina>
-    <codigodeproyecto xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">Maquetación de páginas web dentro del proyecto Biscaytik</codigodeproyecto>
-    <fechafinestimado xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
-    <TaxCatchAll xmlns="06fec347-a373-485e-bb4f-f611040a1dd3" xsi:nil="true"/>
-    <Cliente xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">209</Cliente>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <fechafinreal xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
-    <Oferta_x0020_Antigua xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4782,28 +4761,44 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Estado xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">En curso</Estado>
+    <Area xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">7</Area>
+    <Acciones xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
+    <sys xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
+    <Sociedad xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
+    <fechadeproyecto xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">2022-07-13T22:00:00+00:00</fechadeproyecto>
+    <OfertaAnterior xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
+    <DocumentSetDescription xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Oferta xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">
+      <Value>5919</Value>
+    </Oferta>
+    <responsableproyecto xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">
+      <UserInfo>
+        <DisplayName>Aitor Roncero Val</DisplayName>
+        <AccountId>927</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </responsableproyecto>
+    <Oficina xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">1</Oficina>
+    <codigodeproyecto xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">Maquetación de páginas web dentro del proyecto Biscaytik</codigodeproyecto>
+    <fechafinestimado xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
+    <TaxCatchAll xmlns="06fec347-a373-485e-bb4f-f611040a1dd3" xsi:nil="true"/>
+    <Cliente xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">209</Cliente>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <fechafinreal xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
+    <Oferta_x0020_Antigua xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C64067D8-2529-40F8-873F-7DCFF29E6C0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5D2ED08-240E-422E-815D-BA2AE63D0B29}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="06fec347-a373-485e-bb4f-f611040a1dd3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4829,9 +4824,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5D2ED08-240E-422E-815D-BA2AE63D0B29}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C64067D8-2529-40F8-873F-7DCFF29E6C0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="06fec347-a373-485e-bb4f-f611040a1dd3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/src/Documentacion/BIS011APPSY-SeguimientoPlanTrabajoDesaHERRIZ-v2.xlsx
+++ b/src/Documentacion/BIS011APPSY-SeguimientoPlanTrabajoDesaHERRIZ-v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgantolin\BiscaytikApp_node-modules-incluido\src\Documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8515182E-BAB6-4A59-BD51-5F4497A91540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A6D7E5-F515-4507-89DC-62D2DEF9BE31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="249">
   <si>
     <t>HITO</t>
   </si>
@@ -749,9 +749,6 @@
     <t xml:space="preserve">ESTADO  (02-09 parta teknei) </t>
   </si>
   <si>
-    <t>Condicionado. Consulta canal</t>
-  </si>
-  <si>
     <t>Finalizado. Rehecho img 100%</t>
   </si>
   <si>
@@ -762,6 +759,30 @@
   </si>
   <si>
     <t>En curso. 1ra prueba hecha.Cuando esté todo el portal revisar acad punto</t>
+  </si>
+  <si>
+    <t>En curso. Seria interesante añadir badge subcategoría</t>
+  </si>
+  <si>
+    <t>Falta funcionalidad compartir, estimación modificar estructura muestra servicios</t>
+  </si>
+  <si>
+    <t>Estimación horas nuevo. Tema tabs</t>
+  </si>
+  <si>
+    <t>contenido. Añadir 1 "diapositiva" más para que se muestre a modo slider. Estimación actual. New BTS5</t>
+  </si>
+  <si>
+    <t>A la espera modificaciones y definición con DESA</t>
+  </si>
+  <si>
+    <t>Condicionado. 1 ejem para todos los tipos (todos contenidos)</t>
+  </si>
+  <si>
+    <t>Condicionado. Dependiente contenidos y decisiones BKTT (todos contenidos)</t>
+  </si>
+  <si>
+    <t>Bloqueado. desarrollado en detalle bar. VALIDACIón , casos de uso</t>
   </si>
 </sst>
 </file>
@@ -2291,8 +2312,8 @@
       <c r="AB30" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="AD30" s="44" t="s">
-        <v>237</v>
+      <c r="AD30" s="43" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:31" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -2363,7 +2384,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="35" spans="1:32" ht="72" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:32" ht="86.4" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
         <v>178</v>
       </c>
@@ -2414,7 +2435,7 @@
         <v>209</v>
       </c>
       <c r="AE35" s="19" t="s">
-        <v>186</v>
+        <v>244</v>
       </c>
       <c r="AF35" s="19" t="s">
         <v>234</v>
@@ -2594,7 +2615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:32" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:32" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A43" s="32" t="s">
         <v>62</v>
       </c>
@@ -2637,10 +2658,7 @@
         <v>223</v>
       </c>
       <c r="AD43" s="44" t="s">
-        <v>221</v>
-      </c>
-      <c r="AE43" s="54" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="AF43" s="19" t="s">
         <v>223</v>
@@ -2674,7 +2692,7 @@
       <c r="AA44" s="47"/>
       <c r="AD44" s="47"/>
     </row>
-    <row r="45" spans="1:32" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:32" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A45" s="50" t="s">
         <v>222</v>
       </c>
@@ -2709,7 +2727,7 @@
         <v>223</v>
       </c>
       <c r="AD45" s="44" t="s">
-        <v>210</v>
+        <v>247</v>
       </c>
       <c r="AE45" s="19" t="s">
         <v>220</v>
@@ -2852,14 +2870,14 @@
       <c r="AB48" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="AD48" s="46" t="s">
-        <v>169</v>
+      <c r="AD48" s="45" t="s">
+        <v>168</v>
       </c>
       <c r="AE48" s="19" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="49" spans="1:32" outlineLevel="2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:32" ht="43.2" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A49" s="33" t="s">
         <v>172</v>
       </c>
@@ -2898,11 +2916,11 @@
       <c r="AB49" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="AD49" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="AE49" s="19" t="s">
-        <v>183</v>
+      <c r="AD49" s="45" t="s">
+        <v>168</v>
+      </c>
+      <c r="AE49" s="55" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="50" spans="1:32" ht="23.4" x14ac:dyDescent="0.3">
@@ -3046,7 +3064,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:32" ht="57.6" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:32" ht="86.4" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="23" t="s">
+        <v>81</v>
+      </c>
       <c r="C60" s="23" t="s">
         <v>81</v>
       </c>
@@ -3093,8 +3114,8 @@
       <c r="AD60" s="43" t="s">
         <v>166</v>
       </c>
-      <c r="AE60" s="19" t="s">
-        <v>212</v>
+      <c r="AE60" s="55" t="s">
+        <v>242</v>
       </c>
       <c r="AF60" s="19" t="s">
         <v>213</v>
@@ -3132,13 +3153,13 @@
         <v>166</v>
       </c>
       <c r="AB61" s="55" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AD61" s="43" t="s">
         <v>166</v>
       </c>
       <c r="AE61" s="55" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="62" spans="1:32" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -3188,10 +3209,10 @@
         <v>189</v>
       </c>
       <c r="AD62" s="43" t="s">
-        <v>238</v>
-      </c>
-      <c r="AE62" s="19" t="s">
-        <v>190</v>
+        <v>237</v>
+      </c>
+      <c r="AE62" s="55" t="s">
+        <v>243</v>
       </c>
       <c r="AF62" s="19" t="s">
         <v>189</v>
@@ -3270,13 +3291,13 @@
         <v>193</v>
       </c>
       <c r="AA64" s="44" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AB64" s="19" t="s">
         <v>214</v>
       </c>
       <c r="AD64" s="44" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AE64" s="19" t="s">
         <v>214</v>
@@ -3455,7 +3476,7 @@
         <v>202</v>
       </c>
       <c r="AD69" s="46" t="s">
-        <v>219</v>
+        <v>248</v>
       </c>
       <c r="AE69" s="19" t="s">
         <v>194</v>
@@ -3571,7 +3592,7 @@
         <v>197</v>
       </c>
       <c r="AD72" s="45" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AE72" s="19" t="s">
         <v>233</v>
@@ -3626,8 +3647,8 @@
       <c r="AB73" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="AD73" s="46" t="s">
-        <v>169</v>
+      <c r="AD73" s="45" t="s">
+        <v>241</v>
       </c>
       <c r="AE73" s="19" t="s">
         <v>232</v>

--- a/src/Documentacion/BIS011APPSY-SeguimientoPlanTrabajoDesaHERRIZ-v2.xlsx
+++ b/src/Documentacion/BIS011APPSY-SeguimientoPlanTrabajoDesaHERRIZ-v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgantolin\BiscaytikApp_node-modules-incluido\src\Documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A6D7E5-F515-4507-89DC-62D2DEF9BE31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA20F13E-2D77-4D22-A24A-EE86CCCBF7C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3771,8 +3771,8 @@
       <c r="AB76" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="AD76" s="46" t="s">
-        <v>169</v>
+      <c r="AD76" s="45" t="s">
+        <v>168</v>
       </c>
       <c r="AE76" s="19" t="s">
         <v>230</v>
@@ -4382,6 +4382,41 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Estado xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">En curso</Estado>
+    <Area xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">7</Area>
+    <Acciones xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
+    <sys xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
+    <Sociedad xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
+    <fechadeproyecto xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">2022-07-13T22:00:00+00:00</fechadeproyecto>
+    <OfertaAnterior xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
+    <DocumentSetDescription xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Oferta xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">
+      <Value>5919</Value>
+    </Oferta>
+    <responsableproyecto xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">
+      <UserInfo>
+        <DisplayName>Aitor Roncero Val</DisplayName>
+        <AccountId>927</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </responsableproyecto>
+    <Oficina xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">1</Oficina>
+    <codigodeproyecto xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">Maquetación de páginas web dentro del proyecto Biscaytik</codigodeproyecto>
+    <fechafinestimado xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
+    <TaxCatchAll xmlns="06fec347-a373-485e-bb4f-f611040a1dd3" xsi:nil="true"/>
+    <Cliente xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">209</Cliente>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <fechafinreal xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
+    <Oferta_x0020_Antigua xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010021AB849DB9524648A8F6CDAE5A42EE85" ma:contentTypeVersion="54" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5cf342e325584cfc73779b32cd8516cb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xmlns:ns3="06fec347-a373-485e-bb4f-f611040a1dd3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="97bec9e280156beb57af844d85b9963b" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -4781,41 +4816,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Estado xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">En curso</Estado>
-    <Area xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">7</Area>
-    <Acciones xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
-    <sys xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
-    <Sociedad xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
-    <fechadeproyecto xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">2022-07-13T22:00:00+00:00</fechadeproyecto>
-    <OfertaAnterior xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
-    <DocumentSetDescription xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Oferta xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">
-      <Value>5919</Value>
-    </Oferta>
-    <responsableproyecto xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">
-      <UserInfo>
-        <DisplayName>Aitor Roncero Val</DisplayName>
-        <AccountId>927</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </responsableproyecto>
-    <Oficina xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">1</Oficina>
-    <codigodeproyecto xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">Maquetación de páginas web dentro del proyecto Biscaytik</codigodeproyecto>
-    <fechafinestimado xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
-    <TaxCatchAll xmlns="06fec347-a373-485e-bb4f-f611040a1dd3" xsi:nil="true"/>
-    <Cliente xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">209</Cliente>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <fechafinreal xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
-    <Oferta_x0020_Antigua xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5D2ED08-240E-422E-815D-BA2AE63D0B29}">
   <ds:schemaRefs>
@@ -4825,6 +4825,24 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C64067D8-2529-40F8-873F-7DCFF29E6C0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="06fec347-a373-485e-bb4f-f611040a1dd3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B271E1E9-4B5A-43C8-93E9-EF9A1A456C27}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4842,22 +4860,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C64067D8-2529-40F8-873F-7DCFF29E6C0A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="06fec347-a373-485e-bb4f-f611040a1dd3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/src/Documentacion/BIS011APPSY-SeguimientoPlanTrabajoDesaHERRIZ-v2.xlsx
+++ b/src/Documentacion/BIS011APPSY-SeguimientoPlanTrabajoDesaHERRIZ-v2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgantolin\BiscaytikApp_node-modules-incluido\src\Documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA20F13E-2D77-4D22-A24A-EE86CCCBF7C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03BD6B9B-D8E6-4B9F-B584-DD4609CA1821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="271">
   <si>
     <t>HITO</t>
   </si>
@@ -245,9 +245,6 @@
     <t>BKTT-Card (en sus diferentes versiones)</t>
   </si>
   <si>
-    <t>3.2</t>
-  </si>
-  <si>
     <t>Maquetación Propuesta Listado &amp; Detalle Evento</t>
   </si>
   <si>
@@ -743,46 +740,115 @@
     <t>B decisión cual utilizar co nªs esfuerzo</t>
   </si>
   <si>
+    <t xml:space="preserve">ESTADO  (02-09 parta teknei) </t>
+  </si>
+  <si>
+    <t>Finalizado. Rehecho img 100%</t>
+  </si>
+  <si>
+    <t>En listados repetido por estructura sitio</t>
+  </si>
+  <si>
+    <t>Condicionado. Revisar tab galería?</t>
+  </si>
+  <si>
+    <t>En curso. Seria interesante añadir badge subcategoría</t>
+  </si>
+  <si>
+    <t>Falta funcionalidad compartir, estimación modificar estructura muestra servicios</t>
+  </si>
+  <si>
+    <t>Estimación horas nuevo. Tema tabs</t>
+  </si>
+  <si>
+    <t>contenido. Añadir 1 "diapositiva" más para que se muestre a modo slider. Estimación actual. New BTS5</t>
+  </si>
+  <si>
+    <t>A la espera modificaciones y definición con DESA</t>
+  </si>
+  <si>
+    <t>Bloqueado. desarrollado en detalle bar. VALIDACIón , casos de uso</t>
+  </si>
+  <si>
+    <t>Detalle Hostelería (ahora 2 restaurantes )</t>
+  </si>
+  <si>
+    <t>(y bares )</t>
+  </si>
+  <si>
+    <t>Finalizado. Está en detalle restaurante. X para poder cerrar</t>
+  </si>
+  <si>
+    <t>En curso. No final. Fase 2</t>
+  </si>
+  <si>
+    <t>Suma y links (15/10/2026)</t>
+  </si>
+  <si>
+    <t>Suma y links</t>
+  </si>
+  <si>
+    <t>85% Finalizado.  Ajustes css</t>
+  </si>
+  <si>
+    <t xml:space="preserve">buscador botón / colapsable menú </t>
+  </si>
+  <si>
+    <t>Validación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTADO  (15-09 parta teknei) </t>
+  </si>
+  <si>
     <t>Finalizado. BG img pero en este ejmplo no procede</t>
   </si>
   <si>
-    <t xml:space="preserve">ESTADO  (02-09 parta teknei) </t>
-  </si>
-  <si>
-    <t>Finalizado. Rehecho img 100%</t>
-  </si>
-  <si>
-    <t>En listados repetido por estructura sitio</t>
-  </si>
-  <si>
-    <t>Condicionado. Revisar tab galería?</t>
-  </si>
-  <si>
-    <t>En curso. 1ra prueba hecha.Cuando esté todo el portal revisar acad punto</t>
-  </si>
-  <si>
-    <t>En curso. Seria interesante añadir badge subcategoría</t>
-  </si>
-  <si>
-    <t>Falta funcionalidad compartir, estimación modificar estructura muestra servicios</t>
-  </si>
-  <si>
-    <t>Estimación horas nuevo. Tema tabs</t>
-  </si>
-  <si>
-    <t>contenido. Añadir 1 "diapositiva" más para que se muestre a modo slider. Estimación actual. New BTS5</t>
-  </si>
-  <si>
-    <t>A la espera modificaciones y definición con DESA</t>
-  </si>
-  <si>
-    <t>Condicionado. 1 ejem para todos los tipos (todos contenidos)</t>
-  </si>
-  <si>
-    <t>Condicionado. Dependiente contenidos y decisiones BKTT (todos contenidos)</t>
-  </si>
-  <si>
-    <t>Bloqueado. desarrollado en detalle bar. VALIDACIón , casos de uso</t>
+    <t>Condicionado. A falta de que coja css</t>
+  </si>
+  <si>
+    <t>Restaurantes</t>
+  </si>
+  <si>
+    <t>Eventos</t>
+  </si>
+  <si>
+    <t>Noticias</t>
+  </si>
+  <si>
+    <t>Patrimonio</t>
+  </si>
+  <si>
+    <t>Alojamiento</t>
+  </si>
+  <si>
+    <t>Bares</t>
+  </si>
+  <si>
+    <t>Rutas</t>
+  </si>
+  <si>
+    <t>Qué ver / playas</t>
+  </si>
+  <si>
+    <t>3.2 LISTADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condicionado. </t>
+  </si>
+  <si>
+    <t>Slider final, si editamos / eliminamos contenidoa antiguos</t>
+  </si>
+  <si>
+    <t>Bloqueado. Fase2</t>
+  </si>
+  <si>
+    <t>Validación? Editar llamada css head</t>
+  </si>
+  <si>
+    <t>80% Finalizado. 1ra prueba hecha.</t>
+  </si>
+  <si>
+    <t>En curso. Ajuste nueva versión 14/10</t>
   </si>
 </sst>
 </file>
@@ -793,7 +859,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -936,8 +1002,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="19">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1046,6 +1128,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8E4BC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92CDDC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE9D9"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1061,7 +1167,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1208,6 +1314,25 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1519,7 +1644,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AF107"/>
+  <dimension ref="A1:AL125"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" outlineLevelRow="2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.33203125" style="49" customWidth="1"/>
@@ -1544,10 +1669,11 @@
     <col min="30" max="30" width="28.6640625" style="19" customWidth="1"/>
     <col min="31" max="31" width="17.5546875" style="19" customWidth="1"/>
     <col min="32" max="32" width="12.88671875" style="19" customWidth="1"/>
+    <col min="33" max="33" width="18.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="22.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:32" ht="216" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:38" ht="22.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:38" ht="216" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1580,70 +1706,88 @@
       </c>
       <c r="K2" s="3"/>
       <c r="L2" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>10</v>
       </c>
       <c r="N2" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="O2" s="35" t="s">
         <v>138</v>
       </c>
-      <c r="O2" s="35" t="s">
+      <c r="P2" s="35" t="s">
         <v>139</v>
       </c>
-      <c r="P2" s="35" t="s">
+      <c r="Q2" s="35" t="s">
         <v>140</v>
       </c>
-      <c r="Q2" s="35" t="s">
-        <v>141</v>
-      </c>
       <c r="R2" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="S2" s="35" t="s">
         <v>148</v>
       </c>
-      <c r="S2" s="35" t="s">
-        <v>149</v>
-      </c>
       <c r="T2" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="U2" s="35" t="s">
         <v>154</v>
       </c>
-      <c r="U2" s="35" t="s">
-        <v>155</v>
-      </c>
       <c r="V2" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="W2" s="35" t="s">
         <v>161</v>
       </c>
-      <c r="W2" s="35" t="s">
-        <v>162</v>
-      </c>
       <c r="X2" s="35" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Y2" s="35" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Z2" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="AA2" s="35" t="s">
+        <v>204</v>
+      </c>
+      <c r="AB2" s="35" t="s">
         <v>180</v>
       </c>
-      <c r="AA2" s="35" t="s">
-        <v>205</v>
-      </c>
-      <c r="AB2" s="35" t="s">
-        <v>181</v>
-      </c>
       <c r="AC2" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="AD2" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="AE2" s="35" t="s">
         <v>180</v>
       </c>
-      <c r="AD2" s="35" t="s">
-        <v>236</v>
-      </c>
-      <c r="AE2" s="35" t="s">
-        <v>181</v>
-      </c>
       <c r="AF2" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="AG2" s="35" t="s">
+        <v>253</v>
+      </c>
+      <c r="AH2" s="35" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="AI2" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ2" s="35" t="s">
+        <v>253</v>
+      </c>
+      <c r="AK2" s="35" t="s">
+        <v>180</v>
+      </c>
+      <c r="AL2" s="35" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A3" s="50">
         <v>0</v>
       </c>
@@ -1672,16 +1816,28 @@
         <v>80</v>
       </c>
       <c r="X3" s="39" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AA3" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="AD3" s="43" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+      <c r="AD3" s="56" t="s">
+        <v>165</v>
+      </c>
+      <c r="AE3" s="33"/>
+      <c r="AF3" s="33"/>
+      <c r="AG3" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AH3" s="19"/>
+      <c r="AI3" s="19"/>
+      <c r="AJ3" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK3" s="19"/>
+      <c r="AL3" s="19"/>
+    </row>
+    <row r="4" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="D4" s="30" t="s">
         <v>13</v>
       </c>
@@ -1700,14 +1856,32 @@
       </c>
       <c r="J4" s="5"/>
       <c r="M4" s="26"/>
-    </row>
-    <row r="5" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AD4" s="33"/>
+      <c r="AE4" s="33"/>
+      <c r="AF4" s="33"/>
+      <c r="AG4" s="19"/>
+      <c r="AH4" s="19"/>
+      <c r="AI4" s="19"/>
+      <c r="AJ4" s="19"/>
+      <c r="AK4" s="19"/>
+      <c r="AL4" s="19"/>
+    </row>
+    <row r="5" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="D5" s="19" t="s">
         <v>16</v>
       </c>
       <c r="M5" s="26"/>
-    </row>
-    <row r="6" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AD5" s="33"/>
+      <c r="AE5" s="33"/>
+      <c r="AF5" s="33"/>
+      <c r="AG5" s="19"/>
+      <c r="AH5" s="19"/>
+      <c r="AI5" s="19"/>
+      <c r="AJ5" s="19"/>
+      <c r="AK5" s="19"/>
+      <c r="AL5" s="19"/>
+    </row>
+    <row r="6" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="D6" s="30" t="s">
         <v>17</v>
       </c>
@@ -1726,14 +1900,32 @@
       </c>
       <c r="J6" s="5"/>
       <c r="M6" s="26"/>
-    </row>
-    <row r="7" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AD6" s="33"/>
+      <c r="AE6" s="33"/>
+      <c r="AF6" s="33"/>
+      <c r="AG6" s="19"/>
+      <c r="AH6" s="19"/>
+      <c r="AI6" s="19"/>
+      <c r="AJ6" s="19"/>
+      <c r="AK6" s="19"/>
+      <c r="AL6" s="19"/>
+    </row>
+    <row r="7" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="D7" s="19" t="s">
         <v>20</v>
       </c>
       <c r="M7" s="26"/>
-    </row>
-    <row r="8" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AD7" s="33"/>
+      <c r="AE7" s="33"/>
+      <c r="AF7" s="33"/>
+      <c r="AG7" s="19"/>
+      <c r="AH7" s="19"/>
+      <c r="AI7" s="19"/>
+      <c r="AJ7" s="19"/>
+      <c r="AK7" s="19"/>
+      <c r="AL7" s="19"/>
+    </row>
+    <row r="8" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="D8" s="31" t="s">
         <v>21</v>
       </c>
@@ -1752,14 +1944,32 @@
       </c>
       <c r="J8" s="5"/>
       <c r="M8" s="26"/>
-    </row>
-    <row r="9" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AD8" s="33"/>
+      <c r="AE8" s="33"/>
+      <c r="AF8" s="33"/>
+      <c r="AG8" s="19"/>
+      <c r="AH8" s="19"/>
+      <c r="AI8" s="19"/>
+      <c r="AJ8" s="19"/>
+      <c r="AK8" s="19"/>
+      <c r="AL8" s="19"/>
+    </row>
+    <row r="9" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="D9" s="19" t="s">
         <v>22</v>
       </c>
       <c r="M9" s="26"/>
-    </row>
-    <row r="10" spans="1:32" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="AD9" s="33"/>
+      <c r="AE9" s="33"/>
+      <c r="AF9" s="33"/>
+      <c r="AG9" s="19"/>
+      <c r="AH9" s="19"/>
+      <c r="AI9" s="19"/>
+      <c r="AJ9" s="19"/>
+      <c r="AK9" s="19"/>
+      <c r="AL9" s="19"/>
+    </row>
+    <row r="10" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A10" s="50">
         <v>1</v>
       </c>
@@ -1782,7 +1992,7 @@
         <v>70</v>
       </c>
       <c r="Q10" s="36" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="U10">
         <v>80</v>
@@ -1793,8 +2003,17 @@
       <c r="W10">
         <v>95</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AD10" s="33"/>
+      <c r="AE10" s="33"/>
+      <c r="AF10" s="33"/>
+      <c r="AG10" s="19"/>
+      <c r="AH10" s="19"/>
+      <c r="AI10" s="19"/>
+      <c r="AJ10" s="19"/>
+      <c r="AK10" s="19"/>
+      <c r="AL10" s="19"/>
+    </row>
+    <row r="11" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A11" s="30" t="s">
         <v>26</v>
       </c>
@@ -1824,16 +2043,28 @@
       </c>
       <c r="M11" s="26"/>
       <c r="X11" s="39" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AA11" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="AD11" s="43" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+      <c r="AD11" s="56" t="s">
+        <v>165</v>
+      </c>
+      <c r="AE11" s="33"/>
+      <c r="AF11" s="33"/>
+      <c r="AG11" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AH11" s="19"/>
+      <c r="AI11" s="19"/>
+      <c r="AJ11" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK11" s="19"/>
+      <c r="AL11" s="19"/>
+    </row>
+    <row r="12" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>30</v>
       </c>
@@ -1847,8 +2078,17 @@
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
       <c r="M12" s="26"/>
-    </row>
-    <row r="13" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AD12" s="33"/>
+      <c r="AE12" s="33"/>
+      <c r="AF12" s="33"/>
+      <c r="AG12" s="19"/>
+      <c r="AH12" s="19"/>
+      <c r="AI12" s="19"/>
+      <c r="AJ12" s="19"/>
+      <c r="AK12" s="19"/>
+      <c r="AL12" s="19"/>
+    </row>
+    <row r="13" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>31</v>
       </c>
@@ -1862,8 +2102,17 @@
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
       <c r="M13" s="26"/>
-    </row>
-    <row r="14" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AD13" s="33"/>
+      <c r="AE13" s="33"/>
+      <c r="AF13" s="33"/>
+      <c r="AG13" s="19"/>
+      <c r="AH13" s="19"/>
+      <c r="AI13" s="19"/>
+      <c r="AJ13" s="19"/>
+      <c r="AK13" s="19"/>
+      <c r="AL13" s="19"/>
+    </row>
+    <row r="14" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>32</v>
       </c>
@@ -1877,8 +2126,17 @@
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
       <c r="M14" s="26"/>
-    </row>
-    <row r="15" spans="1:32" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AD14" s="33"/>
+      <c r="AE14" s="33"/>
+      <c r="AF14" s="33"/>
+      <c r="AG14" s="19"/>
+      <c r="AH14" s="19"/>
+      <c r="AI14" s="19"/>
+      <c r="AJ14" s="19"/>
+      <c r="AK14" s="19"/>
+      <c r="AL14" s="19"/>
+    </row>
+    <row r="15" spans="1:38" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>33</v>
       </c>
@@ -1893,22 +2151,34 @@
       <c r="J15" s="6"/>
       <c r="M15" s="26"/>
       <c r="X15" s="37" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Y15" s="19" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AA15" s="44" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AB15" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="AD15" s="43" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="16" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+      <c r="AD15" s="56" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE15" s="33"/>
+      <c r="AF15" s="33"/>
+      <c r="AG15" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="AH15" s="19"/>
+      <c r="AI15" s="19"/>
+      <c r="AJ15" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="AK15" s="19"/>
+      <c r="AL15" s="19"/>
+    </row>
+    <row r="16" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>34</v>
       </c>
@@ -1922,8 +2192,17 @@
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
       <c r="M16" s="26"/>
-    </row>
-    <row r="17" spans="1:31" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AD16" s="33"/>
+      <c r="AE16" s="33"/>
+      <c r="AF16" s="33"/>
+      <c r="AG16" s="19"/>
+      <c r="AH16" s="19"/>
+      <c r="AI16" s="19"/>
+      <c r="AJ16" s="19"/>
+      <c r="AK16" s="19"/>
+      <c r="AL16" s="19"/>
+    </row>
+    <row r="17" spans="1:38" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A17" s="30" t="s">
         <v>35</v>
       </c>
@@ -1946,19 +2225,35 @@
       <c r="J17" s="6"/>
       <c r="M17" s="26"/>
       <c r="X17" s="38" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Y17" s="19" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AA17" s="45" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD17" s="43" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="18" spans="1:31" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>215</v>
+      </c>
+      <c r="AD17" s="56" t="s">
+        <v>165</v>
+      </c>
+      <c r="AE17" s="33"/>
+      <c r="AF17" s="33"/>
+      <c r="AG17" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AH17" s="19"/>
+      <c r="AI17" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="AJ17" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK17" s="19"/>
+      <c r="AL17" s="19" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="18" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
         <v>36</v>
       </c>
@@ -1972,8 +2267,17 @@
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
       <c r="M18" s="26"/>
-    </row>
-    <row r="19" spans="1:31" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AD18" s="33"/>
+      <c r="AE18" s="33"/>
+      <c r="AF18" s="33"/>
+      <c r="AG18" s="19"/>
+      <c r="AH18" s="19"/>
+      <c r="AI18" s="19"/>
+      <c r="AJ18" s="19"/>
+      <c r="AK18" s="19"/>
+      <c r="AL18" s="19"/>
+    </row>
+    <row r="19" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>37</v>
       </c>
@@ -1987,8 +2291,17 @@
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
       <c r="M19" s="26"/>
-    </row>
-    <row r="20" spans="1:31" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AD19" s="33"/>
+      <c r="AE19" s="33"/>
+      <c r="AF19" s="33"/>
+      <c r="AG19" s="19"/>
+      <c r="AH19" s="19"/>
+      <c r="AI19" s="19"/>
+      <c r="AJ19" s="19"/>
+      <c r="AK19" s="19"/>
+      <c r="AL19" s="19"/>
+    </row>
+    <row r="20" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
         <v>38</v>
       </c>
@@ -2003,13 +2316,22 @@
       <c r="J20" s="6"/>
       <c r="M20" s="26"/>
       <c r="S20" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="U20" s="36" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="21" spans="1:31" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+      <c r="AD20" s="33"/>
+      <c r="AE20" s="33"/>
+      <c r="AF20" s="33"/>
+      <c r="AG20" s="19"/>
+      <c r="AH20" s="19"/>
+      <c r="AI20" s="19"/>
+      <c r="AJ20" s="19"/>
+      <c r="AK20" s="19"/>
+      <c r="AL20" s="19"/>
+    </row>
+    <row r="21" spans="1:38" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A21" s="30" t="s">
         <v>39</v>
       </c>
@@ -2038,22 +2360,41 @@
         <v>95</v>
       </c>
       <c r="X21" s="39" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AA21" s="43" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AB21" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="AD21" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="AE21" s="19" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="22" spans="1:31" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+        <v>206</v>
+      </c>
+      <c r="AD21" s="56" t="s">
+        <v>165</v>
+      </c>
+      <c r="AE21" s="33" t="s">
+        <v>206</v>
+      </c>
+      <c r="AF21" s="33"/>
+      <c r="AG21" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AH21" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="AI21" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="AJ21" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK21" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="AL21" s="19" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="22" spans="1:38" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>40</v>
       </c>
@@ -2067,8 +2408,17 @@
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
       <c r="M22" s="26"/>
-    </row>
-    <row r="23" spans="1:31" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AD22" s="33"/>
+      <c r="AE22" s="33"/>
+      <c r="AF22" s="33"/>
+      <c r="AG22" s="19"/>
+      <c r="AH22" s="19"/>
+      <c r="AI22" s="19"/>
+      <c r="AJ22" s="19"/>
+      <c r="AK22" s="19"/>
+      <c r="AL22" s="19"/>
+    </row>
+    <row r="23" spans="1:38" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A23" s="30" t="s">
         <v>41</v>
       </c>
@@ -2094,16 +2444,32 @@
         <v>60</v>
       </c>
       <c r="X23" s="40" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AA23" s="45" t="s">
-        <v>206</v>
-      </c>
-      <c r="AD23" s="45" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="24" spans="1:31" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+      <c r="AD23" s="57" t="s">
+        <v>205</v>
+      </c>
+      <c r="AE23" s="33"/>
+      <c r="AF23" s="33"/>
+      <c r="AG23" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AH23" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="AI23" s="19"/>
+      <c r="AJ23" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AK23" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="AL23" s="19"/>
+    </row>
+    <row r="24" spans="1:38" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
         <v>42</v>
       </c>
@@ -2112,13 +2478,22 @@
       </c>
       <c r="M24" s="26"/>
       <c r="S24" t="s">
+        <v>155</v>
+      </c>
+      <c r="U24" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="U24" s="36" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="25" spans="1:31" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AD24" s="33"/>
+      <c r="AE24" s="33"/>
+      <c r="AF24" s="33"/>
+      <c r="AG24" s="19"/>
+      <c r="AH24" s="19"/>
+      <c r="AI24" s="19"/>
+      <c r="AJ24" s="19"/>
+      <c r="AK24" s="19"/>
+      <c r="AL24" s="19"/>
+    </row>
+    <row r="25" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A25" s="30" t="s">
         <v>44</v>
       </c>
@@ -2151,7 +2526,7 @@
         <v>70</v>
       </c>
       <c r="Q25" s="36" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="S25">
         <v>80</v>
@@ -2160,18 +2535,27 @@
         <v>70</v>
       </c>
       <c r="V25" s="36" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="W25">
         <v>75</v>
       </c>
-    </row>
-    <row r="26" spans="1:31" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="AD25" s="33"/>
+      <c r="AE25" s="33"/>
+      <c r="AF25" s="33"/>
+      <c r="AG25" s="19"/>
+      <c r="AH25" s="19"/>
+      <c r="AI25" s="19"/>
+      <c r="AJ25" s="19"/>
+      <c r="AK25" s="19"/>
+      <c r="AL25" s="19"/>
+    </row>
+    <row r="26" spans="1:38" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
@@ -2179,16 +2563,32 @@
       <c r="I26" s="9"/>
       <c r="M26" s="26"/>
       <c r="X26" s="39" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AA26" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="AD26" s="43" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="27" spans="1:31" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+      <c r="AD26" s="56" t="s">
+        <v>165</v>
+      </c>
+      <c r="AE26" s="33"/>
+      <c r="AF26" s="33"/>
+      <c r="AG26" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AH26" s="19"/>
+      <c r="AI26" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="AJ26" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK26" s="19"/>
+      <c r="AL26" s="19" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="27" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A27" s="30" t="s">
         <v>45</v>
       </c>
@@ -2209,22 +2609,31 @@
       </c>
       <c r="M27" s="26"/>
       <c r="S27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="U27" s="36" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="W27" s="36" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="X27" s="19"/>
-    </row>
-    <row r="28" spans="1:31" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="AD27" s="33"/>
+      <c r="AE27" s="33"/>
+      <c r="AF27" s="33"/>
+      <c r="AG27" s="19"/>
+      <c r="AH27" s="19"/>
+      <c r="AI27" s="19"/>
+      <c r="AJ27" s="19"/>
+      <c r="AK27" s="19"/>
+      <c r="AL27" s="19"/>
+    </row>
+    <row r="28" spans="1:38" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A28" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
@@ -2232,16 +2641,32 @@
       <c r="I28" s="9"/>
       <c r="M28" s="26"/>
       <c r="X28" s="42" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AA28" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="AD28" s="43" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="29" spans="1:31" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+      <c r="AD28" s="56" t="s">
+        <v>165</v>
+      </c>
+      <c r="AE28" s="33"/>
+      <c r="AF28" s="33"/>
+      <c r="AG28" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AH28" s="19"/>
+      <c r="AI28" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="AJ28" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK28" s="19"/>
+      <c r="AL28" s="19" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="29" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A29" s="30" t="s">
         <v>46</v>
       </c>
@@ -2262,16 +2687,32 @@
       </c>
       <c r="M29" s="26"/>
       <c r="X29" s="39" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AA29" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="AD29" s="43" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="30" spans="1:31" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+      <c r="AD29" s="56" t="s">
+        <v>165</v>
+      </c>
+      <c r="AE29" s="33"/>
+      <c r="AF29" s="33"/>
+      <c r="AG29" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AH29" s="19"/>
+      <c r="AI29" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="AJ29" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK29" s="19"/>
+      <c r="AL29" s="19" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="30" spans="1:38" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A30" s="30" t="s">
         <v>47</v>
       </c>
@@ -2292,31 +2733,47 @@
       </c>
       <c r="M30" s="26"/>
       <c r="S30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="U30" s="36" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="W30" s="36" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="X30" s="37" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Y30" s="19" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AA30" s="44" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AB30" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD30" s="43" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="31" spans="1:31" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>207</v>
+      </c>
+      <c r="AD30" s="58" t="s">
+        <v>255</v>
+      </c>
+      <c r="AE30" s="33"/>
+      <c r="AF30" s="33"/>
+      <c r="AG30" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AH30" s="19"/>
+      <c r="AI30" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="AJ30" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK30" s="19"/>
+      <c r="AL30" s="19" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="31" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A31" s="13" t="s">
         <v>48</v>
       </c>
@@ -2329,16 +2786,32 @@
       <c r="I31" s="9"/>
       <c r="M31" s="26"/>
       <c r="X31" s="39" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AA31" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="AD31" s="39" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="32" spans="1:31" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+      <c r="AD31" s="59" t="s">
+        <v>165</v>
+      </c>
+      <c r="AE31" s="33"/>
+      <c r="AF31" s="33"/>
+      <c r="AG31" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="AH31" s="19"/>
+      <c r="AI31" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="AJ31" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK31" s="19"/>
+      <c r="AL31" s="19" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="32" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A32" s="19" t="s">
         <v>49</v>
       </c>
@@ -2349,8 +2822,17 @@
       <c r="W32">
         <v>70</v>
       </c>
-    </row>
-    <row r="33" spans="1:32" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="AD32" s="33"/>
+      <c r="AE32" s="33"/>
+      <c r="AF32" s="33"/>
+      <c r="AG32" s="19"/>
+      <c r="AH32" s="19"/>
+      <c r="AI32" s="19"/>
+      <c r="AJ32" s="19"/>
+      <c r="AK32" s="19"/>
+      <c r="AL32" s="19"/>
+    </row>
+    <row r="33" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A33" s="50">
         <v>2</v>
       </c>
@@ -2363,8 +2845,17 @@
       <c r="M33" s="28">
         <v>94</v>
       </c>
-    </row>
-    <row r="34" spans="1:32" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AD33" s="33"/>
+      <c r="AE33" s="33"/>
+      <c r="AF33" s="33"/>
+      <c r="AG33" s="19"/>
+      <c r="AH33" s="19"/>
+      <c r="AI33" s="19"/>
+      <c r="AJ33" s="19"/>
+      <c r="AK33" s="19"/>
+      <c r="AL33" s="19"/>
+    </row>
+    <row r="34" spans="1:38" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A34" s="30" t="s">
         <v>52</v>
       </c>
@@ -2381,15 +2872,24 @@
       <c r="J34" s="6"/>
       <c r="M34" s="26"/>
       <c r="Q34" s="36" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="35" spans="1:32" ht="86.4" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+      <c r="AD34" s="33"/>
+      <c r="AE34" s="33"/>
+      <c r="AF34" s="33"/>
+      <c r="AG34" s="19"/>
+      <c r="AH34" s="19"/>
+      <c r="AI34" s="19"/>
+      <c r="AJ34" s="19"/>
+      <c r="AK34" s="19"/>
+      <c r="AL34" s="19"/>
+    </row>
+    <row r="35" spans="1:38" ht="86.4" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>18</v>
@@ -2405,43 +2905,57 @@
       <c r="J35" s="6"/>
       <c r="M35" s="26"/>
       <c r="Q35" s="36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="S35" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="U35" s="36" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="X35" s="37" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Y35" s="19" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Z35" s="19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AA35" s="46" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AB35" s="19" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AC35" s="19" t="s">
-        <v>234</v>
-      </c>
-      <c r="AD35" s="46" t="s">
-        <v>209</v>
-      </c>
-      <c r="AE35" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="AF35" s="19" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="36" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>233</v>
+      </c>
+      <c r="AD35" s="60" t="s">
+        <v>208</v>
+      </c>
+      <c r="AE35" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="AF35" s="33" t="s">
+        <v>233</v>
+      </c>
+      <c r="AG35" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AH35" s="19"/>
+      <c r="AI35" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="AJ35" s="45" t="s">
+        <v>270</v>
+      </c>
+      <c r="AK35" s="19"/>
+      <c r="AL35" s="19" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="36" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
         <v>54</v>
       </c>
@@ -2465,7 +2979,7 @@
         <v>50</v>
       </c>
       <c r="Q36" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="T36">
         <v>80</v>
@@ -2476,8 +2990,17 @@
       <c r="W36">
         <v>80</v>
       </c>
-    </row>
-    <row r="37" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AD36" s="33"/>
+      <c r="AE36" s="33"/>
+      <c r="AF36" s="33"/>
+      <c r="AG36" s="19"/>
+      <c r="AH36" s="19"/>
+      <c r="AI36" s="19"/>
+      <c r="AJ36" s="19"/>
+      <c r="AK36" s="19"/>
+      <c r="AL36" s="19"/>
+    </row>
+    <row r="37" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
         <v>55</v>
       </c>
@@ -2500,8 +3023,17 @@
       <c r="Q37">
         <v>5</v>
       </c>
-    </row>
-    <row r="38" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AD37" s="33"/>
+      <c r="AE37" s="33"/>
+      <c r="AF37" s="33"/>
+      <c r="AG37" s="19"/>
+      <c r="AH37" s="19"/>
+      <c r="AI37" s="19"/>
+      <c r="AJ37" s="19"/>
+      <c r="AK37" s="19"/>
+      <c r="AL37" s="19"/>
+    </row>
+    <row r="38" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
         <v>56</v>
       </c>
@@ -2516,10 +3048,19 @@
       <c r="J38" s="6"/>
       <c r="M38" s="26"/>
       <c r="Q38" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="39" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+      <c r="AD38" s="33"/>
+      <c r="AE38" s="33"/>
+      <c r="AF38" s="33"/>
+      <c r="AG38" s="19"/>
+      <c r="AH38" s="19"/>
+      <c r="AI38" s="19"/>
+      <c r="AJ38" s="19"/>
+      <c r="AK38" s="19"/>
+      <c r="AL38" s="19"/>
+    </row>
+    <row r="39" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
         <v>57</v>
       </c>
@@ -2542,8 +3083,17 @@
       <c r="Q39">
         <v>5</v>
       </c>
-    </row>
-    <row r="40" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AD39" s="33"/>
+      <c r="AE39" s="33"/>
+      <c r="AF39" s="33"/>
+      <c r="AG39" s="19"/>
+      <c r="AH39" s="19"/>
+      <c r="AI39" s="19"/>
+      <c r="AJ39" s="19"/>
+      <c r="AK39" s="19"/>
+      <c r="AL39" s="19"/>
+    </row>
+    <row r="40" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>58</v>
       </c>
@@ -2566,8 +3116,17 @@
       <c r="Q40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AD40" s="33"/>
+      <c r="AE40" s="33"/>
+      <c r="AF40" s="33"/>
+      <c r="AG40" s="19"/>
+      <c r="AH40" s="19"/>
+      <c r="AI40" s="19"/>
+      <c r="AJ40" s="19"/>
+      <c r="AK40" s="19"/>
+      <c r="AL40" s="19"/>
+    </row>
+    <row r="41" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
         <v>59</v>
       </c>
@@ -2590,8 +3149,17 @@
       <c r="Q41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:32" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="AD41" s="33"/>
+      <c r="AE41" s="33"/>
+      <c r="AF41" s="33"/>
+      <c r="AG41" s="19"/>
+      <c r="AH41" s="19"/>
+      <c r="AI41" s="19"/>
+      <c r="AJ41" s="19"/>
+      <c r="AK41" s="19"/>
+      <c r="AL41" s="19"/>
+    </row>
+    <row r="42" spans="1:38" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>60</v>
       </c>
@@ -2614,8 +3182,17 @@
       <c r="Q42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:32" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AD42" s="33"/>
+      <c r="AE42" s="33"/>
+      <c r="AF42" s="33"/>
+      <c r="AG42" s="19"/>
+      <c r="AH42" s="19"/>
+      <c r="AI42" s="19"/>
+      <c r="AJ42" s="19"/>
+      <c r="AK42" s="19"/>
+      <c r="AL42" s="19"/>
+    </row>
+    <row r="43" spans="1:38" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A43" s="32" t="s">
         <v>62</v>
       </c>
@@ -2639,7 +3216,7 @@
       <c r="J43" s="6"/>
       <c r="M43" s="26"/>
       <c r="Q43" s="36" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="T43">
         <v>50</v>
@@ -2649,22 +3226,33 @@
       </c>
       <c r="X43" s="41"/>
       <c r="AA43" s="44" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AB43" s="54" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AC43" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="AD43" s="44" t="s">
-        <v>246</v>
-      </c>
-      <c r="AF43" s="19" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="44" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>222</v>
+      </c>
+      <c r="AD43" s="58" t="s">
+        <v>220</v>
+      </c>
+      <c r="AE43" s="33"/>
+      <c r="AF43" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="AG43" s="47"/>
+      <c r="AH43" s="19"/>
+      <c r="AI43" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="AJ43" s="47"/>
+      <c r="AK43" s="19"/>
+      <c r="AL43" s="19" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="44" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C44" s="25" t="s">
         <v>63</v>
       </c>
@@ -2683,18 +3271,26 @@
       </c>
       <c r="M44" s="26"/>
       <c r="Q44" s="36" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="U44" s="36" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="X44" s="41"/>
       <c r="AA44" s="47"/>
-      <c r="AD44" s="47"/>
-    </row>
-    <row r="45" spans="1:32" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="AD44" s="61"/>
+      <c r="AE44" s="33"/>
+      <c r="AF44" s="33"/>
+      <c r="AG44" s="47"/>
+      <c r="AH44" s="19"/>
+      <c r="AI44" s="19"/>
+      <c r="AJ44" s="47"/>
+      <c r="AK44" s="19"/>
+      <c r="AL44" s="19"/>
+    </row>
+    <row r="45" spans="1:38" ht="72" x14ac:dyDescent="0.3">
       <c r="A45" s="50" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B45" s="16" t="s">
         <v>64</v>
@@ -2715,28 +3311,46 @@
         <v>60</v>
       </c>
       <c r="X45" s="40" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AA45" s="44" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AB45" s="19" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AC45" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="AD45" s="44" t="s">
-        <v>247</v>
-      </c>
-      <c r="AE45" s="19" t="s">
-        <v>220</v>
-      </c>
-      <c r="AF45" s="19" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="46" spans="1:32" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
+        <v>222</v>
+      </c>
+      <c r="AD45" s="58" t="s">
+        <v>209</v>
+      </c>
+      <c r="AE45" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="AF45" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="AG45" s="44" t="s">
+        <v>265</v>
+      </c>
+      <c r="AH45" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="AI45" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="AJ45" s="44" t="s">
+        <v>265</v>
+      </c>
+      <c r="AK45" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="AL45" s="19" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="46" spans="1:38" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A46" s="19" t="s">
         <v>66</v>
       </c>
@@ -2758,31 +3372,46 @@
         <v>50</v>
       </c>
       <c r="S46" s="36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="T46">
         <v>50</v>
       </c>
       <c r="U46" s="36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="X46" s="39" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AA46" s="43" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AB46" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="AD46" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="AE46" s="19" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="47" spans="1:32" outlineLevel="2" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+      <c r="AD46" s="56" t="s">
+        <v>165</v>
+      </c>
+      <c r="AE46" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="AF46" s="33"/>
+      <c r="AG46" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AH46" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="AI46" s="19"/>
+      <c r="AJ46" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK46" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="AL46" s="19"/>
+    </row>
+    <row r="47" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A47" s="19" t="s">
         <v>67</v>
       </c>
@@ -2804,31 +3433,46 @@
         <v>100</v>
       </c>
       <c r="S47" s="36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="T47">
         <v>100</v>
       </c>
       <c r="U47" s="36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="X47" s="39" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AA47" s="43" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AB47" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="AD47" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="AE47" s="19" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="48" spans="1:32" ht="43.2" outlineLevel="2" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+      <c r="AD47" s="56" t="s">
+        <v>165</v>
+      </c>
+      <c r="AE47" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="AF47" s="33"/>
+      <c r="AG47" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AH47" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="AI47" s="19"/>
+      <c r="AJ47" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK47" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="AL47" s="19"/>
+    </row>
+    <row r="48" spans="1:38" ht="86.4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A48" s="33" t="s">
         <v>68</v>
       </c>
@@ -2859,892 +3503,752 @@
         <v>10</v>
       </c>
       <c r="X48" s="37" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Y48" s="19" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AA48" s="46" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AB48" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="AD48" s="45" t="s">
-        <v>168</v>
-      </c>
-      <c r="AE48" s="19" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="49" spans="1:32" ht="43.2" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A49" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="D49" s="33" t="s">
-        <v>172</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="AD48" s="57" t="s">
+        <v>167</v>
+      </c>
+      <c r="AE48" s="33" t="s">
+        <v>186</v>
+      </c>
+      <c r="AF48" s="33"/>
+      <c r="AG48" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AH48" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="AI48" s="19"/>
+      <c r="AJ48" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK48" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="AL48" s="19"/>
+    </row>
+    <row r="49" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A49" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="D49" s="33"/>
       <c r="E49" s="6"/>
       <c r="M49" s="26"/>
-      <c r="P49">
+      <c r="X49" s="37"/>
+      <c r="AA49" s="46"/>
+      <c r="AD49" s="57"/>
+      <c r="AE49" s="33"/>
+      <c r="AF49" s="33"/>
+      <c r="AG49" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AH49" s="19"/>
+      <c r="AI49" s="19"/>
+      <c r="AJ49" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK49" s="19"/>
+      <c r="AL49" s="19"/>
+    </row>
+    <row r="50" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A50" s="32" t="s">
+        <v>258</v>
+      </c>
+      <c r="D50" s="33"/>
+      <c r="E50" s="6"/>
+      <c r="M50" s="26"/>
+      <c r="Y50"/>
+      <c r="Z50"/>
+      <c r="AA50"/>
+      <c r="AB50"/>
+      <c r="AC50"/>
+      <c r="AD50"/>
+      <c r="AE50"/>
+      <c r="AF50"/>
+      <c r="AG50" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AH50" s="19"/>
+      <c r="AI50" s="19"/>
+      <c r="AJ50" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK50" s="19"/>
+      <c r="AL50" s="19"/>
+    </row>
+    <row r="51" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A51" s="32" t="s">
+        <v>259</v>
+      </c>
+      <c r="D51" s="33"/>
+      <c r="E51" s="6"/>
+      <c r="M51" s="26"/>
+      <c r="Y51"/>
+      <c r="Z51"/>
+      <c r="AA51"/>
+      <c r="AB51"/>
+      <c r="AC51"/>
+      <c r="AD51"/>
+      <c r="AE51"/>
+      <c r="AF51"/>
+      <c r="AG51" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AH51" s="19"/>
+      <c r="AI51" s="19"/>
+      <c r="AJ51" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK51" s="19"/>
+      <c r="AL51" s="19"/>
+    </row>
+    <row r="52" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A52" s="32" t="s">
+        <v>262</v>
+      </c>
+      <c r="D52" s="33"/>
+      <c r="E52" s="6"/>
+      <c r="M52" s="26"/>
+      <c r="Y52"/>
+      <c r="Z52"/>
+      <c r="AA52"/>
+      <c r="AB52"/>
+      <c r="AC52"/>
+      <c r="AD52"/>
+      <c r="AE52"/>
+      <c r="AF52"/>
+      <c r="AG52" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AH52" s="19"/>
+      <c r="AI52" s="19"/>
+      <c r="AJ52" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK52" s="19"/>
+      <c r="AL52" s="19"/>
+    </row>
+    <row r="53" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A53" s="32" t="s">
+        <v>260</v>
+      </c>
+      <c r="D53" s="33"/>
+      <c r="E53" s="6"/>
+      <c r="M53" s="26"/>
+      <c r="Y53"/>
+      <c r="Z53"/>
+      <c r="AA53"/>
+      <c r="AB53"/>
+      <c r="AC53"/>
+      <c r="AD53"/>
+      <c r="AE53"/>
+      <c r="AF53"/>
+      <c r="AG53" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AH53" s="19"/>
+      <c r="AI53" s="19"/>
+      <c r="AJ53" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK53" s="19"/>
+      <c r="AL53" s="19"/>
+    </row>
+    <row r="54" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A54" s="32" t="s">
+        <v>256</v>
+      </c>
+      <c r="D54" s="33"/>
+      <c r="E54" s="6"/>
+      <c r="M54" s="26"/>
+      <c r="Y54"/>
+      <c r="Z54"/>
+      <c r="AA54"/>
+      <c r="AB54"/>
+      <c r="AC54"/>
+      <c r="AD54"/>
+      <c r="AE54"/>
+      <c r="AF54"/>
+      <c r="AG54" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AH54" s="19"/>
+      <c r="AI54" s="19"/>
+      <c r="AJ54" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK54" s="19"/>
+      <c r="AL54" s="19"/>
+    </row>
+    <row r="55" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A55" s="32" t="s">
+        <v>261</v>
+      </c>
+      <c r="D55" s="33"/>
+      <c r="E55" s="6"/>
+      <c r="M55" s="26"/>
+      <c r="Y55"/>
+      <c r="Z55"/>
+      <c r="AA55"/>
+      <c r="AB55"/>
+      <c r="AC55"/>
+      <c r="AD55"/>
+      <c r="AE55"/>
+      <c r="AF55"/>
+      <c r="AG55" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AH55" s="19"/>
+      <c r="AI55" s="19"/>
+      <c r="AJ55" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK55" s="19"/>
+      <c r="AL55" s="19"/>
+    </row>
+    <row r="56" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A56" s="32" t="s">
+        <v>263</v>
+      </c>
+      <c r="D56" s="33"/>
+      <c r="E56" s="6"/>
+      <c r="M56" s="26"/>
+      <c r="Y56"/>
+      <c r="Z56"/>
+      <c r="AA56"/>
+      <c r="AB56"/>
+      <c r="AC56"/>
+      <c r="AD56"/>
+      <c r="AE56"/>
+      <c r="AF56"/>
+      <c r="AG56" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AH56" s="19"/>
+      <c r="AI56" s="19"/>
+      <c r="AJ56" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AK56" s="19"/>
+      <c r="AL56" s="19"/>
+    </row>
+    <row r="57" spans="1:38" ht="72" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A57" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="D57" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="E57" s="6"/>
+      <c r="M57" s="26"/>
+      <c r="P57">
         <v>70</v>
       </c>
-      <c r="Q49">
+      <c r="Q57">
         <v>0</v>
       </c>
-      <c r="R49">
+      <c r="R57">
         <v>50</v>
       </c>
-      <c r="S49">
+      <c r="S57">
         <v>5</v>
       </c>
-      <c r="T49">
+      <c r="T57">
         <v>50</v>
       </c>
-      <c r="U49">
+      <c r="U57">
         <v>5</v>
       </c>
-      <c r="X49" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y49" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="AA49" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="AB49" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="AD49" s="45" t="s">
+      <c r="X57" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="AE49" s="55" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="50" spans="1:32" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A50" s="50" t="s">
+      <c r="Y57" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="AA57" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB57" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="AD57" s="57" t="s">
+        <v>167</v>
+      </c>
+      <c r="AE57" s="62" t="s">
+        <v>242</v>
+      </c>
+      <c r="AF57" s="33"/>
+      <c r="AG57" s="45" t="s">
+        <v>247</v>
+      </c>
+      <c r="AH57" s="55" t="s">
+        <v>242</v>
+      </c>
+      <c r="AI57" s="19"/>
+      <c r="AJ57" s="45" t="s">
+        <v>247</v>
+      </c>
+      <c r="AK57" s="55" t="s">
+        <v>242</v>
+      </c>
+      <c r="AL57" s="19"/>
+    </row>
+    <row r="58" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A58" s="50" t="s">
+        <v>264</v>
+      </c>
+      <c r="B58" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="B50" s="16" t="s">
+      <c r="C58" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="C50" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="E50" s="6" t="s">
+      <c r="E58" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="11" t="s">
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="I50" s="9" t="s">
+      <c r="I58" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="K50" s="6"/>
-      <c r="L50" s="6"/>
-      <c r="M50" s="28">
+      <c r="K58" s="6"/>
+      <c r="L58" s="6"/>
+      <c r="M58" s="28">
         <v>87</v>
       </c>
-      <c r="W50" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="51" spans="1:32" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="D51" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="M51" s="26"/>
-      <c r="R51">
-        <v>10</v>
-      </c>
-      <c r="S51" s="36" t="s">
-        <v>145</v>
-      </c>
-      <c r="V51">
-        <v>60</v>
-      </c>
-      <c r="W51" s="36" t="s">
-        <v>145</v>
-      </c>
-      <c r="X51" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y51" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="AA51" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="AB51" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="AD51" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="AE51" s="19" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="52" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="D52" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="M52" s="26"/>
-    </row>
-    <row r="53" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="D53" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="M53" s="26"/>
-    </row>
-    <row r="54" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="D54" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="M54" s="26"/>
-    </row>
-    <row r="55" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="D55" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="M55" s="26"/>
-    </row>
-    <row r="56" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="D56" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="M56" s="26"/>
-    </row>
-    <row r="57" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="D57" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="M57" s="26"/>
-    </row>
-    <row r="58" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="D58" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="M58" s="26"/>
-      <c r="P58">
-        <v>5</v>
-      </c>
-      <c r="Q58">
-        <v>0</v>
-      </c>
-      <c r="R58">
-        <v>5</v>
-      </c>
-      <c r="S58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="D59" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="M59" s="26"/>
-      <c r="P59">
-        <v>5</v>
-      </c>
-      <c r="Q59">
-        <v>0</v>
-      </c>
-      <c r="R59">
-        <v>5</v>
-      </c>
-      <c r="S59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:32" ht="86.4" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="C60" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="D60" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>18</v>
-      </c>
+      <c r="W58" t="s">
+        <v>163</v>
+      </c>
+      <c r="AD58" s="33"/>
+      <c r="AE58" s="33"/>
+      <c r="AF58" s="33"/>
+      <c r="AG58" s="19"/>
+      <c r="AH58" s="19"/>
+      <c r="AI58" s="19"/>
+      <c r="AJ58" s="19"/>
+      <c r="AK58" s="19"/>
+      <c r="AL58" s="19"/>
+    </row>
+    <row r="59" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A59" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="D59" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="E59" s="6"/>
+      <c r="F59" s="6"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="11"/>
+      <c r="I59" s="9"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="6"/>
+      <c r="M59" s="28"/>
+      <c r="N59" s="28"/>
+      <c r="AD59" s="33"/>
+      <c r="AE59" s="33"/>
+      <c r="AF59" s="33"/>
+      <c r="AG59" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AH59" s="19"/>
+      <c r="AI59" s="19"/>
+      <c r="AJ59" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK59" s="19"/>
+      <c r="AL59" s="19"/>
+    </row>
+    <row r="60" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A60" s="32" t="s">
+        <v>258</v>
+      </c>
+      <c r="D60" s="32" t="s">
+        <v>258</v>
+      </c>
+      <c r="E60" s="6"/>
       <c r="F60" s="6"/>
       <c r="G60" s="6"/>
-      <c r="H60" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="I60" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K60" s="12"/>
-      <c r="L60" s="12"/>
-      <c r="P60">
-        <v>5</v>
-      </c>
-      <c r="Q60">
-        <v>0</v>
-      </c>
-      <c r="S60" t="s">
-        <v>152</v>
-      </c>
-      <c r="W60" t="s">
-        <v>165</v>
-      </c>
-      <c r="X60" s="38" t="s">
+      <c r="H60" s="11"/>
+      <c r="I60" s="9"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="6"/>
+      <c r="M60" s="28"/>
+      <c r="AD60" s="33"/>
+      <c r="AE60" s="33"/>
+      <c r="AF60" s="33"/>
+      <c r="AG60" s="45" t="s">
         <v>167</v>
       </c>
-      <c r="AA60" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="AB60" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="AC60" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="AD60" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="AE60" s="55" t="s">
-        <v>242</v>
-      </c>
-      <c r="AF60" s="19" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="61" spans="1:32" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C61" s="13"/>
-      <c r="D61" s="13" t="s">
-        <v>83</v>
+      <c r="AH60" s="19"/>
+      <c r="AI60" s="19"/>
+      <c r="AJ60" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK60" s="19"/>
+      <c r="AL60" s="19"/>
+    </row>
+    <row r="61" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A61" s="32" t="s">
+        <v>259</v>
+      </c>
+      <c r="D61" s="32" t="s">
+        <v>259</v>
       </c>
       <c r="E61" s="6"/>
       <c r="F61" s="6"/>
       <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
+      <c r="H61" s="11"/>
       <c r="I61" s="9"/>
-      <c r="K61" s="12"/>
-      <c r="L61" s="12"/>
-      <c r="M61" s="26"/>
-      <c r="R61">
-        <v>90</v>
-      </c>
-      <c r="S61" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="X61" s="38" t="s">
+      <c r="K61" s="6"/>
+      <c r="L61" s="6"/>
+      <c r="M61" s="28"/>
+      <c r="AD61" s="33"/>
+      <c r="AE61" s="33"/>
+      <c r="AF61" s="33"/>
+      <c r="AG61" s="45" t="s">
         <v>167</v>
       </c>
-      <c r="Y61" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="AA61" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="AB61" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="AD61" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="AE61" s="55" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="62" spans="1:32" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="C62" s="13"/>
-      <c r="D62" s="13" t="s">
-        <v>192</v>
+      <c r="AH61" s="19"/>
+      <c r="AI61" s="19"/>
+      <c r="AJ61" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK61" s="19"/>
+      <c r="AL61" s="19"/>
+    </row>
+    <row r="62" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A62" s="32" t="s">
+        <v>262</v>
+      </c>
+      <c r="D62" s="32" t="s">
+        <v>262</v>
       </c>
       <c r="E62" s="6"/>
       <c r="F62" s="6"/>
       <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
+      <c r="H62" s="11"/>
       <c r="I62" s="9"/>
-      <c r="K62" s="12"/>
-      <c r="L62" s="12"/>
-      <c r="M62" s="26"/>
-      <c r="P62">
-        <v>10</v>
-      </c>
-      <c r="Q62">
-        <v>0</v>
-      </c>
-      <c r="R62">
-        <v>30</v>
-      </c>
-      <c r="S62">
-        <v>5</v>
-      </c>
-      <c r="X62" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="Y62" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="Z62" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="AA62" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="AB62" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="AC62" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="AD62" s="43" t="s">
-        <v>237</v>
-      </c>
-      <c r="AE62" s="55" t="s">
-        <v>243</v>
-      </c>
-      <c r="AF62" s="19" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="63" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C63" s="13"/>
-      <c r="D63" s="13" t="s">
-        <v>84</v>
+      <c r="K62" s="6"/>
+      <c r="L62" s="6"/>
+      <c r="M62" s="28"/>
+      <c r="AD62" s="33"/>
+      <c r="AE62" s="33"/>
+      <c r="AF62" s="33"/>
+      <c r="AG62" s="19"/>
+      <c r="AH62" s="19"/>
+      <c r="AI62" s="19"/>
+      <c r="AJ62" s="19"/>
+      <c r="AK62" s="19"/>
+      <c r="AL62" s="19"/>
+    </row>
+    <row r="63" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A63" s="32" t="s">
+        <v>260</v>
+      </c>
+      <c r="D63" s="32" t="s">
+        <v>260</v>
       </c>
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
       <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
+      <c r="H63" s="11"/>
       <c r="I63" s="9"/>
-      <c r="K63" s="12"/>
-      <c r="L63" s="12"/>
-      <c r="M63" s="26"/>
-      <c r="P63">
-        <v>50</v>
-      </c>
-      <c r="Q63">
-        <v>0</v>
-      </c>
-      <c r="R63">
-        <v>40</v>
-      </c>
-      <c r="S63">
-        <v>5</v>
-      </c>
-      <c r="X63" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="AA63" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="AD63" s="43" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="64" spans="1:32" ht="72" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C64" s="13"/>
-      <c r="D64" s="13" t="s">
-        <v>85</v>
+      <c r="K63" s="6"/>
+      <c r="L63" s="6"/>
+      <c r="M63" s="28"/>
+      <c r="AD63" s="33"/>
+      <c r="AE63" s="33"/>
+      <c r="AF63" s="33"/>
+      <c r="AG63" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AH63" s="19"/>
+      <c r="AI63" s="19"/>
+      <c r="AJ63" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK63" s="19"/>
+      <c r="AL63" s="19"/>
+    </row>
+    <row r="64" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A64" s="32" t="s">
+        <v>256</v>
+      </c>
+      <c r="D64" s="32" t="s">
+        <v>256</v>
       </c>
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
       <c r="G64" s="6"/>
-      <c r="H64" s="6"/>
+      <c r="H64" s="11"/>
       <c r="I64" s="9"/>
-      <c r="K64" s="12"/>
-      <c r="L64" s="12"/>
-      <c r="M64" s="26"/>
-      <c r="P64">
-        <v>5</v>
-      </c>
-      <c r="Q64">
-        <v>0</v>
-      </c>
-      <c r="R64">
-        <v>30</v>
-      </c>
-      <c r="S64" s="36" t="s">
-        <v>147</v>
-      </c>
-      <c r="X64" s="38" t="s">
+      <c r="K64" s="6"/>
+      <c r="L64" s="6"/>
+      <c r="M64" s="28"/>
+      <c r="AD64" s="33"/>
+      <c r="AE64" s="33"/>
+      <c r="AF64" s="33"/>
+      <c r="AG64" s="45" t="s">
         <v>167</v>
       </c>
-      <c r="Y64" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="AA64" s="44" t="s">
-        <v>239</v>
-      </c>
-      <c r="AB64" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="AD64" s="44" t="s">
-        <v>239</v>
-      </c>
-      <c r="AE64" s="19" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="65" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C65" s="13"/>
-      <c r="D65" s="13" t="s">
-        <v>86</v>
+      <c r="AH64" s="19"/>
+      <c r="AI64" s="19"/>
+      <c r="AJ64" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK64" s="19"/>
+      <c r="AL64" s="19"/>
+    </row>
+    <row r="65" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A65" s="32" t="s">
+        <v>261</v>
+      </c>
+      <c r="D65" s="32" t="s">
+        <v>261</v>
       </c>
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
       <c r="G65" s="6"/>
-      <c r="H65" s="6"/>
+      <c r="H65" s="11"/>
       <c r="I65" s="9"/>
-      <c r="K65" s="12"/>
-      <c r="L65" s="12"/>
-      <c r="M65" s="26"/>
-      <c r="R65">
-        <v>40</v>
-      </c>
-      <c r="S65">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="66" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C66" s="13"/>
-      <c r="D66" s="13" t="s">
-        <v>80</v>
+      <c r="K65" s="6"/>
+      <c r="L65" s="6"/>
+      <c r="M65" s="28"/>
+      <c r="AD65" s="33"/>
+      <c r="AE65" s="33"/>
+      <c r="AF65" s="33"/>
+      <c r="AG65" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AH65" s="19"/>
+      <c r="AI65" s="19"/>
+      <c r="AJ65" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK65" s="19"/>
+      <c r="AL65" s="19"/>
+    </row>
+    <row r="66" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A66" s="32" t="s">
+        <v>263</v>
+      </c>
+      <c r="D66" s="32" t="s">
+        <v>263</v>
       </c>
       <c r="E66" s="6"/>
       <c r="F66" s="6"/>
       <c r="G66" s="6"/>
-      <c r="H66" s="6"/>
-      <c r="J66" s="9"/>
-      <c r="M66" s="26"/>
-      <c r="P66">
+      <c r="H66" s="11"/>
+      <c r="I66" s="9"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="6"/>
+      <c r="M66" s="28"/>
+      <c r="AD66" s="33"/>
+      <c r="AE66" s="33"/>
+      <c r="AF66" s="33"/>
+      <c r="AG66" s="19"/>
+      <c r="AH66" s="19"/>
+      <c r="AI66" s="19"/>
+      <c r="AJ66" s="19"/>
+      <c r="AK66" s="19"/>
+      <c r="AL66" s="19"/>
+    </row>
+    <row r="67" spans="1:38" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="D67" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="M67" s="26"/>
+      <c r="R67">
+        <v>10</v>
+      </c>
+      <c r="S67" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="V67">
+        <v>60</v>
+      </c>
+      <c r="W67" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="X67" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y67" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="AA67" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB67" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="AD67" s="60" t="s">
+        <v>168</v>
+      </c>
+      <c r="AE67" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="AF67" s="33"/>
+      <c r="AG67" s="46" t="s">
+        <v>267</v>
+      </c>
+      <c r="AH67" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="AI67" s="19"/>
+      <c r="AJ67" s="46" t="s">
+        <v>267</v>
+      </c>
+      <c r="AK67" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="AL67" s="19"/>
+    </row>
+    <row r="68" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D68" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="M68" s="26"/>
+      <c r="AG68" s="19"/>
+      <c r="AH68" s="19"/>
+      <c r="AI68" s="19"/>
+      <c r="AJ68" s="19"/>
+      <c r="AK68" s="19"/>
+      <c r="AL68" s="19"/>
+    </row>
+    <row r="69" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D69" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="M69" s="26"/>
+      <c r="AG69" s="19"/>
+      <c r="AH69" s="19"/>
+      <c r="AI69" s="19"/>
+      <c r="AJ69" s="19"/>
+      <c r="AK69" s="19"/>
+      <c r="AL69" s="19"/>
+    </row>
+    <row r="70" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D70" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="M70" s="26"/>
+      <c r="AG70" s="19"/>
+      <c r="AH70" s="19"/>
+      <c r="AI70" s="19"/>
+      <c r="AJ70" s="19"/>
+      <c r="AK70" s="19"/>
+      <c r="AL70" s="19"/>
+    </row>
+    <row r="71" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D71" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="M71" s="26"/>
+      <c r="AG71" s="19"/>
+      <c r="AH71" s="19"/>
+      <c r="AI71" s="19"/>
+      <c r="AJ71" s="19"/>
+      <c r="AK71" s="19"/>
+      <c r="AL71" s="19"/>
+    </row>
+    <row r="72" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D72" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="M72" s="26"/>
+      <c r="AG72" s="19"/>
+      <c r="AH72" s="19"/>
+      <c r="AI72" s="19"/>
+      <c r="AJ72" s="19"/>
+      <c r="AK72" s="19"/>
+      <c r="AL72" s="19"/>
+    </row>
+    <row r="73" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D73" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="M73" s="26"/>
+      <c r="AG73" s="19"/>
+      <c r="AH73" s="19"/>
+      <c r="AI73" s="19"/>
+      <c r="AJ73" s="19"/>
+      <c r="AK73" s="19"/>
+      <c r="AL73" s="19"/>
+    </row>
+    <row r="74" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D74" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="M74" s="26"/>
+      <c r="P74">
         <v>5</v>
       </c>
-      <c r="Q66">
+      <c r="Q74">
         <v>0</v>
       </c>
-      <c r="R66">
-        <v>10</v>
-      </c>
-      <c r="S66">
+      <c r="R74">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="1:32" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="C67" s="13"/>
-      <c r="D67" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="E67" s="6"/>
-      <c r="F67" s="6"/>
-      <c r="G67" s="6"/>
-      <c r="H67" s="6"/>
-      <c r="J67" s="9"/>
-      <c r="M67" s="26"/>
-      <c r="X67" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="Y67" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z67" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="AA67" s="46" t="s">
-        <v>171</v>
-      </c>
-      <c r="AB67" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="AC67" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="AD67" s="46" t="s">
-        <v>171</v>
-      </c>
-      <c r="AE67" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="AF67" s="19" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="68" spans="1:32" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="C68" s="13"/>
-      <c r="D68" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E68" s="6"/>
-      <c r="F68" s="6"/>
-      <c r="G68" s="6"/>
-      <c r="H68" s="6"/>
-      <c r="J68" s="9"/>
-      <c r="M68" s="26"/>
-      <c r="S68" s="36" t="s">
-        <v>145</v>
-      </c>
-      <c r="X68" s="37" t="s">
-        <v>173</v>
-      </c>
-      <c r="Y68" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z68" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="AA68" s="46" t="s">
-        <v>173</v>
-      </c>
-      <c r="AB68" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="AC68" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="AD68" s="46" t="s">
-        <v>173</v>
-      </c>
-      <c r="AE68" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="AF68" s="19" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="69" spans="1:32" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C69" s="13"/>
-      <c r="D69" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="E69" s="6"/>
-      <c r="F69" s="6"/>
-      <c r="G69" s="6"/>
-      <c r="H69" s="6"/>
-      <c r="J69" s="9"/>
-      <c r="M69" s="26"/>
-      <c r="S69" s="36" t="s">
-        <v>145</v>
-      </c>
-      <c r="X69" s="37" t="s">
-        <v>219</v>
-      </c>
-      <c r="Y69" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z69" s="19" t="s">
-        <v>202</v>
-      </c>
-      <c r="AA69" s="46" t="s">
-        <v>219</v>
-      </c>
-      <c r="AB69" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="AC69" s="19" t="s">
-        <v>202</v>
-      </c>
-      <c r="AD69" s="46" t="s">
-        <v>248</v>
-      </c>
-      <c r="AE69" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="AF69" s="19" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="70" spans="1:32" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A70" s="50">
-        <v>4</v>
-      </c>
-      <c r="B70" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="C70" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="M70" s="28">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="71" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="49" t="s">
-        <v>217</v>
-      </c>
-      <c r="C71" s="27" t="s">
-        <v>217</v>
-      </c>
-      <c r="D71" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="E71" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F71" s="6"/>
-      <c r="G71" s="6"/>
-      <c r="H71" s="6"/>
-      <c r="J71" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="M71" s="26"/>
-      <c r="P71">
-        <v>20</v>
-      </c>
-      <c r="Q71">
+      <c r="S74">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="19"/>
+      <c r="AH74" s="19"/>
+      <c r="AI74" s="19"/>
+      <c r="AJ74" s="19"/>
+      <c r="AK74" s="19"/>
+      <c r="AL74" s="19"/>
+    </row>
+    <row r="75" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D75" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="M75" s="26"/>
+      <c r="P75">
         <v>5</v>
       </c>
-      <c r="R71">
-        <v>50</v>
-      </c>
-      <c r="S71">
-        <v>10</v>
-      </c>
-      <c r="X71" s="40" t="s">
-        <v>168</v>
-      </c>
-      <c r="AA71" s="45" t="s">
-        <v>168</v>
-      </c>
-      <c r="AD71" s="45" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="72" spans="1:32" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="49" t="s">
-        <v>218</v>
-      </c>
-      <c r="C72" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="D72" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="E72" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F72" s="6"/>
-      <c r="G72" s="6"/>
-      <c r="H72" s="6"/>
-      <c r="J72" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="M72" s="26"/>
-      <c r="P72">
-        <v>10</v>
-      </c>
-      <c r="Q72">
+      <c r="Q75">
         <v>0</v>
       </c>
-      <c r="R72">
-        <v>10</v>
-      </c>
-      <c r="S72">
+      <c r="R75">
+        <v>5</v>
+      </c>
+      <c r="S75">
         <v>0</v>
       </c>
-      <c r="X72" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y72" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z72" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="AA72" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="AB72" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="AC72" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="AD72" s="45" t="s">
-        <v>240</v>
-      </c>
-      <c r="AE72" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="AF72" s="19" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="73" spans="1:32" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="C73" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="D73" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="E73" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F73" s="6"/>
-      <c r="G73" s="6"/>
-      <c r="H73" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="J73" s="6"/>
-      <c r="K73" s="12"/>
-      <c r="L73" s="12"/>
-      <c r="M73" s="26"/>
-      <c r="P73">
-        <v>10</v>
-      </c>
-      <c r="Q73">
-        <v>0</v>
-      </c>
-      <c r="R73">
-        <v>10</v>
-      </c>
-      <c r="S73">
-        <v>0</v>
-      </c>
-      <c r="X73" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y73" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="AA73" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="AB73" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="AD73" s="45" t="s">
-        <v>241</v>
-      </c>
-      <c r="AE73" s="19" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="74" spans="1:32" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="B74" s="15"/>
-      <c r="C74" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="D74" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="E74" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F74" s="6"/>
-      <c r="G74" s="6"/>
-      <c r="H74" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="I74" s="6"/>
-      <c r="J74" s="12"/>
-      <c r="M74" s="26"/>
-      <c r="X74" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y74" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="AA74" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="AB74" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="AD74" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="AE74" s="19" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="75" spans="1:32" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="30" t="s">
-        <v>177</v>
-      </c>
-      <c r="B75" s="15"/>
-      <c r="C75" s="23" t="s">
-        <v>177</v>
-      </c>
-      <c r="D75" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E75" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F75" s="10"/>
-      <c r="G75" s="10"/>
-      <c r="H75" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="I75" s="15"/>
-      <c r="J75" s="10"/>
-      <c r="K75" s="13"/>
-      <c r="L75" s="13"/>
-      <c r="M75" s="26"/>
-      <c r="X75" s="38" t="s">
-        <v>167</v>
-      </c>
-      <c r="AA75" s="44" t="s">
-        <v>167</v>
-      </c>
-      <c r="AC75" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="AD75" s="44" t="s">
-        <v>167</v>
-      </c>
-      <c r="AF75" s="19" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="76" spans="1:32" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B76" s="15"/>
+      <c r="AG75" s="19"/>
+      <c r="AH75" s="19"/>
+      <c r="AI75" s="19"/>
+      <c r="AJ75" s="19"/>
+      <c r="AK75" s="19"/>
+      <c r="AL75" s="19"/>
+    </row>
+    <row r="76" spans="1:38" ht="115.2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="23" t="s">
+        <v>80</v>
+      </c>
       <c r="C76" s="23" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>18</v>
@@ -3754,618 +4258,1581 @@
       <c r="H76" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="I76" s="6"/>
-      <c r="J76" s="6"/>
+      <c r="I76" s="9" t="s">
+        <v>15</v>
+      </c>
       <c r="K76" s="12"/>
       <c r="L76" s="12"/>
-      <c r="M76" s="26"/>
-      <c r="X76" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y76" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="AA76" s="46" t="s">
-        <v>169</v>
+      <c r="P76">
+        <v>5</v>
+      </c>
+      <c r="Q76">
+        <v>0</v>
+      </c>
+      <c r="S76" t="s">
+        <v>151</v>
+      </c>
+      <c r="W76" t="s">
+        <v>164</v>
+      </c>
+      <c r="X76" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="AA76" s="43" t="s">
+        <v>165</v>
       </c>
       <c r="AB76" s="19" t="s">
-        <v>230</v>
-      </c>
-      <c r="AD76" s="45" t="s">
-        <v>168</v>
-      </c>
-      <c r="AE76" s="19" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="77" spans="1:32" ht="63" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="B77" s="15"/>
-      <c r="C77" s="23" t="s">
-        <v>103</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="AC76" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="AG76" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AH76" s="55" t="s">
+        <v>239</v>
+      </c>
+      <c r="AI76" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ76" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK76" s="55" t="s">
+        <v>239</v>
+      </c>
+      <c r="AL76" s="19" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="77" spans="1:38" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C77" s="13"/>
       <c r="D77" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="E77" s="6" t="s">
-        <v>18</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="E77" s="6"/>
       <c r="F77" s="6"/>
       <c r="G77" s="6"/>
-      <c r="H77" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="I77" s="6"/>
-      <c r="J77" s="6"/>
-      <c r="K77" s="17"/>
-      <c r="L77" s="17"/>
+      <c r="H77" s="6"/>
+      <c r="I77" s="9"/>
+      <c r="K77" s="12"/>
+      <c r="L77" s="12"/>
       <c r="M77" s="26"/>
-      <c r="X77" s="37" t="s">
-        <v>169</v>
+      <c r="R77">
+        <v>90</v>
+      </c>
+      <c r="S77" s="36" t="s">
+        <v>152</v>
+      </c>
+      <c r="X77" s="38" t="s">
+        <v>166</v>
       </c>
       <c r="Y77" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z77" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="AA77" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="AB77" s="53">
-        <v>46309</v>
-      </c>
-      <c r="AC77" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="AD77" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="AE77" s="53">
-        <v>46309</v>
-      </c>
-      <c r="AF77" s="19" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="78" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="48"/>
-      <c r="B78" s="18"/>
+        <v>183</v>
+      </c>
+      <c r="AA77" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AB77" s="55" t="s">
+        <v>236</v>
+      </c>
+      <c r="AG77" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AH77" s="55" t="s">
+        <v>236</v>
+      </c>
+      <c r="AI77" s="19"/>
+      <c r="AJ77" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK77" s="55" t="s">
+        <v>236</v>
+      </c>
+      <c r="AL77" s="19"/>
+    </row>
+    <row r="78" spans="1:38" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="C78" s="13"/>
       <c r="D78" s="13" t="s">
-        <v>105</v>
+        <v>191</v>
       </c>
       <c r="E78" s="6"/>
       <c r="F78" s="6"/>
       <c r="G78" s="6"/>
       <c r="H78" s="6"/>
-      <c r="I78" s="6"/>
-      <c r="J78" s="6"/>
-      <c r="K78" s="17"/>
-      <c r="L78" s="17"/>
+      <c r="I78" s="9"/>
+      <c r="K78" s="12"/>
+      <c r="L78" s="12"/>
       <c r="M78" s="26"/>
-      <c r="X78" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="AA78" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="AD78" s="46" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="79" spans="1:32" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="C79" s="23" t="s">
-        <v>106</v>
-      </c>
+      <c r="P78">
+        <v>10</v>
+      </c>
+      <c r="Q78">
+        <v>0</v>
+      </c>
+      <c r="R78">
+        <v>30</v>
+      </c>
+      <c r="S78">
+        <v>5</v>
+      </c>
+      <c r="X78" s="42" t="s">
+        <v>190</v>
+      </c>
+      <c r="Y78" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="Z78" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="AA78" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AB78" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="AC78" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="AG78" s="43" t="s">
+        <v>235</v>
+      </c>
+      <c r="AH78" s="55" t="s">
+        <v>240</v>
+      </c>
+      <c r="AI78" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="AJ78" s="43" t="s">
+        <v>235</v>
+      </c>
+      <c r="AK78" s="55" t="s">
+        <v>240</v>
+      </c>
+      <c r="AL78" s="19" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="79" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C79" s="13"/>
       <c r="D79" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="E79" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F79" s="12"/>
-      <c r="G79" s="12"/>
-      <c r="H79" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="I79" s="19"/>
-      <c r="J79" s="12"/>
-      <c r="K79" s="17"/>
-      <c r="L79" s="17"/>
+        <v>83</v>
+      </c>
+      <c r="E79" s="6"/>
+      <c r="F79" s="6"/>
+      <c r="G79" s="6"/>
+      <c r="H79" s="6"/>
+      <c r="I79" s="9"/>
+      <c r="K79" s="12"/>
+      <c r="L79" s="12"/>
       <c r="M79" s="26"/>
-      <c r="X79" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y79" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="Z79" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="AA79" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="AB79" s="53">
-        <v>46314</v>
-      </c>
-      <c r="AC79" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="AD79" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="AE79" s="53">
-        <v>46314</v>
-      </c>
-      <c r="AF79" s="19" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="80" spans="1:32" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="C80" s="23" t="s">
-        <v>108</v>
-      </c>
+      <c r="P79">
+        <v>50</v>
+      </c>
+      <c r="Q79">
+        <v>0</v>
+      </c>
+      <c r="R79">
+        <v>40</v>
+      </c>
+      <c r="S79">
+        <v>5</v>
+      </c>
+      <c r="X79" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="AA79" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AG79" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AH79" s="19"/>
+      <c r="AI79" s="19"/>
+      <c r="AJ79" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK79" s="19"/>
+      <c r="AL79" s="19"/>
+    </row>
+    <row r="80" spans="1:38" ht="72" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C80" s="13"/>
       <c r="D80" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="E80" s="6" t="s">
-        <v>18</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="E80" s="6"/>
       <c r="F80" s="6"/>
       <c r="G80" s="6"/>
-      <c r="H80" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="J80" s="6"/>
-      <c r="K80" s="17"/>
-      <c r="L80" s="17"/>
+      <c r="H80" s="6"/>
+      <c r="I80" s="9"/>
+      <c r="K80" s="12"/>
+      <c r="L80" s="12"/>
       <c r="M80" s="26"/>
-      <c r="X80" s="37" t="s">
-        <v>169</v>
+      <c r="P80">
+        <v>5</v>
+      </c>
+      <c r="Q80">
+        <v>0</v>
+      </c>
+      <c r="R80">
+        <v>30</v>
+      </c>
+      <c r="S80" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="X80" s="38" t="s">
+        <v>166</v>
       </c>
       <c r="Y80" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="Z80" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="AA80" s="46" t="s">
-        <v>169</v>
+        <v>192</v>
+      </c>
+      <c r="AA80" s="44" t="s">
+        <v>237</v>
       </c>
       <c r="AB80" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="AC80" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="AD80" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="AE80" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="AF80" s="19" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="81" spans="1:32" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C81" s="16" t="s">
-        <v>110</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="AG80" s="44" t="s">
+        <v>237</v>
+      </c>
+      <c r="AH80" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="AI80" s="19"/>
+      <c r="AJ80" s="44" t="s">
+        <v>237</v>
+      </c>
+      <c r="AK80" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="AL80" s="19"/>
+    </row>
+    <row r="81" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C81" s="13"/>
       <c r="D81" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E81" s="6" t="s">
-        <v>18</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="E81" s="6"/>
       <c r="F81" s="6"/>
       <c r="G81" s="6"/>
-      <c r="H81" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="I81" s="6"/>
-      <c r="J81" s="6"/>
-      <c r="K81" s="6"/>
-      <c r="L81" s="6"/>
+      <c r="H81" s="6"/>
+      <c r="I81" s="9"/>
+      <c r="K81" s="12"/>
+      <c r="L81" s="12"/>
       <c r="M81" s="26"/>
-      <c r="P81">
+      <c r="R81">
+        <v>40</v>
+      </c>
+      <c r="S81">
+        <v>10</v>
+      </c>
+      <c r="AG81" s="19"/>
+      <c r="AH81" s="19"/>
+      <c r="AI81" s="19"/>
+      <c r="AJ81" s="19"/>
+      <c r="AK81" s="19"/>
+      <c r="AL81" s="19"/>
+    </row>
+    <row r="82" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C82" s="13"/>
+      <c r="D82" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E82" s="6"/>
+      <c r="F82" s="6"/>
+      <c r="G82" s="6"/>
+      <c r="H82" s="6"/>
+      <c r="J82" s="9"/>
+      <c r="M82" s="26"/>
+      <c r="P82">
         <v>5</v>
       </c>
-      <c r="S81" t="s">
-        <v>151</v>
-      </c>
-      <c r="X81" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="AA81" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="AB81" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="AC81" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="AD81" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="AE81" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="AF81" s="19" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="82" spans="1:32" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A82" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="B82" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="C82" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="M82" s="28">
-        <v>156</v>
-      </c>
-      <c r="X82" s="37" t="s">
-        <v>204</v>
-      </c>
-      <c r="AA82" s="46" t="s">
-        <v>204</v>
-      </c>
-      <c r="AD82" s="46" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="83" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B83" s="18"/>
-      <c r="C83" s="16" t="s">
-        <v>114</v>
-      </c>
+      <c r="Q82">
+        <v>0</v>
+      </c>
+      <c r="R82">
+        <v>10</v>
+      </c>
+      <c r="S82">
+        <v>5</v>
+      </c>
+      <c r="AG82" s="19"/>
+      <c r="AH82" s="19"/>
+      <c r="AI82" s="19"/>
+      <c r="AJ82" s="19"/>
+      <c r="AK82" s="19"/>
+      <c r="AL82" s="19"/>
+    </row>
+    <row r="83" spans="1:38" ht="72" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C83" s="13"/>
       <c r="D83" s="13" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="E83" s="6"/>
       <c r="F83" s="6"/>
       <c r="G83" s="6"/>
-      <c r="H83" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="J83" s="6"/>
-      <c r="K83" s="6"/>
-      <c r="L83" s="6"/>
+      <c r="H83" s="6"/>
+      <c r="J83" s="9"/>
       <c r="M83" s="26"/>
       <c r="X83" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
+      </c>
+      <c r="Y83" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z83" s="19" t="s">
+        <v>194</v>
       </c>
       <c r="AA83" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="AD83" s="46" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="84" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B84" s="18"/>
-      <c r="C84" s="16" t="s">
-        <v>117</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="AB83" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="AC83" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="AG83" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="AH83" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI83" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="AJ83" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK83" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="AL83" s="19" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="84" spans="1:38" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C84" s="13"/>
       <c r="D84" s="13" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="E84" s="6"/>
       <c r="F84" s="6"/>
       <c r="G84" s="6"/>
-      <c r="H84" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="J84" s="6"/>
-      <c r="K84" s="6"/>
-      <c r="L84" s="6"/>
+      <c r="H84" s="6"/>
+      <c r="J84" s="9"/>
       <c r="M84" s="26"/>
+      <c r="S84" s="36" t="s">
+        <v>144</v>
+      </c>
       <c r="X84" s="37" t="s">
-        <v>169</v>
+        <v>172</v>
+      </c>
+      <c r="Y84" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z84" s="19" t="s">
+        <v>195</v>
       </c>
       <c r="AA84" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="AD84" s="46" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="85" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A85"/>
-      <c r="B85" s="18"/>
-      <c r="C85"/>
+        <v>172</v>
+      </c>
+      <c r="AB84" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="AC84" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="AG84" s="46" t="s">
+        <v>172</v>
+      </c>
+      <c r="AH84" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI84" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="AJ84" s="46" t="s">
+        <v>172</v>
+      </c>
+      <c r="AK84" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="AL84" s="19" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="85" spans="1:38" ht="100.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C85" s="13"/>
       <c r="D85" s="13" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="E85" s="6"/>
       <c r="F85" s="6"/>
       <c r="G85" s="6"/>
-      <c r="H85" s="21"/>
-      <c r="J85" s="6"/>
-      <c r="K85" s="6"/>
-      <c r="L85" s="6"/>
+      <c r="H85" s="6"/>
+      <c r="J85" s="9"/>
       <c r="M85" s="26"/>
-    </row>
-    <row r="86" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A86"/>
-      <c r="B86" s="18"/>
-      <c r="C86"/>
-      <c r="D86" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="E86" s="6"/>
-      <c r="F86" s="6"/>
-      <c r="G86" s="6"/>
-      <c r="H86" s="21"/>
-      <c r="J86" s="6"/>
-      <c r="K86" s="6"/>
-      <c r="L86" s="6"/>
-      <c r="M86" s="26"/>
-    </row>
-    <row r="87" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A87"/>
-      <c r="B87" s="18"/>
-      <c r="C87"/>
-      <c r="D87" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="E87" s="6"/>
+      <c r="S85" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="X85" s="37" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y85" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z85" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="AA85" s="46" t="s">
+        <v>218</v>
+      </c>
+      <c r="AB85" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="AC85" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="AG85" s="46" t="s">
+        <v>243</v>
+      </c>
+      <c r="AH85" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI85" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="AJ85" s="46" t="s">
+        <v>243</v>
+      </c>
+      <c r="AK85" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="AL85" s="19" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="86" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A86" s="50">
+        <v>4</v>
+      </c>
+      <c r="B86" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C86" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="M86" s="28">
+        <v>106</v>
+      </c>
+      <c r="AG86" s="19"/>
+      <c r="AH86" s="19"/>
+      <c r="AI86" s="19"/>
+      <c r="AJ86" s="19"/>
+      <c r="AK86" s="19"/>
+      <c r="AL86" s="19"/>
+    </row>
+    <row r="87" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="49" t="s">
+        <v>216</v>
+      </c>
+      <c r="C87" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="D87" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>18</v>
+      </c>
       <c r="F87" s="6"/>
       <c r="G87" s="6"/>
-      <c r="H87" s="21"/>
-      <c r="J87" s="6"/>
-      <c r="K87" s="6"/>
-      <c r="L87" s="6"/>
+      <c r="H87" s="6"/>
+      <c r="J87" s="14" t="s">
+        <v>92</v>
+      </c>
       <c r="M87" s="26"/>
-    </row>
-    <row r="88" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A88"/>
-      <c r="B88" s="18"/>
-      <c r="C88"/>
+      <c r="P87">
+        <v>20</v>
+      </c>
+      <c r="Q87">
+        <v>5</v>
+      </c>
+      <c r="R87">
+        <v>50</v>
+      </c>
+      <c r="S87">
+        <v>10</v>
+      </c>
+      <c r="X87" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="AA87" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AG87" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AH87" s="19"/>
+      <c r="AI87" s="19"/>
+      <c r="AJ87" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK87" s="19"/>
+      <c r="AL87" s="19"/>
+    </row>
+    <row r="88" spans="1:38" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="49" t="s">
+        <v>217</v>
+      </c>
+      <c r="C88" s="27" t="s">
+        <v>217</v>
+      </c>
       <c r="D88" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="E88" s="6"/>
+        <v>93</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>18</v>
+      </c>
       <c r="F88" s="6"/>
       <c r="G88" s="6"/>
-      <c r="H88" s="21"/>
-      <c r="J88" s="6"/>
-      <c r="K88" s="6"/>
-      <c r="L88" s="6"/>
+      <c r="H88" s="6"/>
+      <c r="J88" s="14" t="s">
+        <v>94</v>
+      </c>
       <c r="M88" s="26"/>
-    </row>
-    <row r="89" spans="1:32" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A89"/>
-      <c r="B89" s="18"/>
-      <c r="C89"/>
+      <c r="P88">
+        <v>10</v>
+      </c>
+      <c r="Q88">
+        <v>0</v>
+      </c>
+      <c r="R88">
+        <v>10</v>
+      </c>
+      <c r="S88">
+        <v>0</v>
+      </c>
+      <c r="X88" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y88" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z88" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA88" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB88" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="AC88" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG88" s="43" t="s">
+        <v>269</v>
+      </c>
+      <c r="AH88" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="AI88" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="AJ88" s="43" t="s">
+        <v>269</v>
+      </c>
+      <c r="AK88" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="AL88" s="19" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="89" spans="1:38" ht="100.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="C89" s="23" t="s">
+        <v>95</v>
+      </c>
       <c r="D89" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="E89" s="6"/>
+        <v>96</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>18</v>
+      </c>
       <c r="F89" s="6"/>
       <c r="G89" s="6"/>
-      <c r="H89" s="21"/>
+      <c r="H89" s="11" t="s">
+        <v>53</v>
+      </c>
       <c r="J89" s="6"/>
-      <c r="K89" s="6"/>
-      <c r="L89" s="6"/>
+      <c r="K89" s="12"/>
+      <c r="L89" s="12"/>
       <c r="M89" s="26"/>
-    </row>
-    <row r="90" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B90" s="18"/>
-      <c r="C90" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="D90" s="13"/>
-      <c r="E90" s="6"/>
+      <c r="P89">
+        <v>10</v>
+      </c>
+      <c r="Q89">
+        <v>0</v>
+      </c>
+      <c r="R89">
+        <v>10</v>
+      </c>
+      <c r="S89">
+        <v>0</v>
+      </c>
+      <c r="X89" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y89" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA89" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB89" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="AG89" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="AH89" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="AI89" s="19"/>
+      <c r="AJ89" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="AK89" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="AL89" s="19"/>
+    </row>
+    <row r="90" spans="1:38" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="B90" s="15"/>
+      <c r="C90" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>18</v>
+      </c>
       <c r="F90" s="6"/>
       <c r="G90" s="6"/>
-      <c r="H90" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="J90" s="6"/>
-      <c r="K90" s="6"/>
-      <c r="L90" s="6"/>
+      <c r="H90" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="I90" s="6"/>
+      <c r="J90" s="12"/>
       <c r="M90" s="26"/>
-      <c r="X90" s="42" t="s">
-        <v>203</v>
-      </c>
-      <c r="AA90" s="45" t="s">
+      <c r="X90" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="AD90" s="45" t="s">
+      <c r="Y90" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA90" s="46" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="91" spans="1:32" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A91" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="B91" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="C91" s="24" t="s">
-        <v>126</v>
-      </c>
-      <c r="M91" s="28">
-        <v>89</v>
-      </c>
-      <c r="X91" s="37" t="s">
-        <v>204</v>
-      </c>
-      <c r="AA91" s="46" t="s">
-        <v>204</v>
-      </c>
-      <c r="AD91" s="46" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="92" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="48"/>
-      <c r="B92" s="18"/>
-      <c r="C92" s="16"/>
-      <c r="D92" s="13" t="s">
-        <v>127</v>
-      </c>
+      <c r="AB90" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="AG90" s="19"/>
+      <c r="AH90" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="AI90" s="19"/>
+      <c r="AJ90" s="19"/>
+      <c r="AK90" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="AL90" s="19"/>
+    </row>
+    <row r="91" spans="1:38" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="B91" s="15"/>
+      <c r="C91" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F91" s="10"/>
+      <c r="G91" s="10"/>
+      <c r="H91" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="I91" s="15"/>
+      <c r="J91" s="10"/>
+      <c r="K91" s="13"/>
+      <c r="L91" s="13"/>
+      <c r="M91" s="26"/>
+      <c r="X91" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="AA91" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AC91" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="AG91" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AH91" s="19"/>
+      <c r="AI91" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="AJ91" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AK91" s="19"/>
+      <c r="AL91" s="19" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="92" spans="1:38" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="B92" s="15"/>
+      <c r="C92" s="23"/>
+      <c r="D92" s="13"/>
       <c r="E92" s="6"/>
-      <c r="F92" s="6"/>
-      <c r="G92" s="6"/>
-      <c r="H92" s="21"/>
-      <c r="J92" s="6"/>
-      <c r="K92" s="6"/>
-      <c r="L92" s="6"/>
+      <c r="F92" s="10"/>
+      <c r="G92" s="10"/>
+      <c r="H92" s="11"/>
+      <c r="I92" s="15"/>
+      <c r="J92" s="10"/>
+      <c r="K92" s="13"/>
+      <c r="L92" s="13"/>
       <c r="M92" s="26"/>
-    </row>
-    <row r="93" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="48"/>
-      <c r="B93" s="18"/>
-      <c r="C93" s="16"/>
+      <c r="X92" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="AA92" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AG92" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AH92" s="19"/>
+      <c r="AI92" s="19"/>
+      <c r="AJ92" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AK92" s="19"/>
+      <c r="AL92" s="19"/>
+    </row>
+    <row r="93" spans="1:38" ht="86.4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="B93" s="15"/>
+      <c r="C93" s="23" t="s">
+        <v>100</v>
+      </c>
       <c r="D93" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="E93" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>18</v>
+      </c>
       <c r="F93" s="6"/>
       <c r="G93" s="6"/>
-      <c r="H93" s="21"/>
+      <c r="H93" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="I93" s="6"/>
       <c r="J93" s="6"/>
-      <c r="K93" s="6"/>
-      <c r="L93" s="6"/>
+      <c r="K93" s="12"/>
+      <c r="L93" s="12"/>
       <c r="M93" s="26"/>
-    </row>
-    <row r="94" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="48"/>
-      <c r="B94" s="18"/>
-      <c r="C94" s="16"/>
+      <c r="X93" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y93" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="AA93" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB93" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="AG93" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AH93" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="AI93" s="19"/>
+      <c r="AJ93" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK93" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="AL93" s="19"/>
+    </row>
+    <row r="94" spans="1:38" ht="63" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="B94" s="15"/>
+      <c r="C94" s="23" t="s">
+        <v>102</v>
+      </c>
       <c r="D94" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="E94" s="6"/>
+        <v>103</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>18</v>
+      </c>
       <c r="F94" s="6"/>
       <c r="G94" s="6"/>
-      <c r="H94" s="21"/>
+      <c r="H94" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="I94" s="6"/>
       <c r="J94" s="6"/>
-      <c r="K94" s="6"/>
-      <c r="L94" s="6"/>
+      <c r="K94" s="17"/>
+      <c r="L94" s="17"/>
       <c r="M94" s="26"/>
-    </row>
-    <row r="95" spans="1:32" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="48"/>
+      <c r="X94" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y94" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="Z94" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="AA94" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB94" s="53">
+        <v>46309</v>
+      </c>
+      <c r="AC94" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="AG94" s="19"/>
+      <c r="AH94" s="53">
+        <v>46309</v>
+      </c>
+      <c r="AI94" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="AJ94" s="19"/>
+      <c r="AK94" s="53">
+        <v>46309</v>
+      </c>
+      <c r="AL94" s="19" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="95" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="13" t="s">
+        <v>104</v>
+      </c>
       <c r="B95" s="18"/>
-      <c r="C95" s="16"/>
       <c r="D95" s="13" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="E95" s="6"/>
       <c r="F95" s="6"/>
       <c r="G95" s="6"/>
-      <c r="H95" s="21"/>
+      <c r="H95" s="6"/>
+      <c r="I95" s="6"/>
       <c r="J95" s="6"/>
-      <c r="K95" s="6"/>
-      <c r="L95" s="6"/>
+      <c r="K95" s="17"/>
+      <c r="L95" s="17"/>
       <c r="M95" s="26"/>
-    </row>
-    <row r="96" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A96" s="48"/>
-      <c r="B96" s="18"/>
-      <c r="C96" s="18"/>
-      <c r="D96" s="18"/>
-      <c r="E96" s="18"/>
-      <c r="F96" s="18"/>
-      <c r="G96" s="18"/>
-      <c r="H96" s="18"/>
+      <c r="X95" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA95" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AG95" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AH95" s="19"/>
+      <c r="AI95" s="19"/>
+      <c r="AJ95" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AK95" s="19"/>
+      <c r="AL95" s="19"/>
+    </row>
+    <row r="96" spans="1:38" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C96" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="D96" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="E96" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F96" s="12"/>
+      <c r="G96" s="12"/>
+      <c r="H96" s="20" t="s">
+        <v>53</v>
+      </c>
       <c r="I96" s="19"/>
       <c r="J96" s="12"/>
       <c r="K96" s="17"/>
       <c r="L96" s="17"/>
-      <c r="M96" s="17"/>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D97" s="12"/>
-      <c r="E97" s="6"/>
+      <c r="M96" s="26"/>
+      <c r="X96" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y96" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="Z96" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="AA96" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB96" s="53">
+        <v>46314</v>
+      </c>
+      <c r="AC96" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="AG96" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AH96" s="53">
+        <v>46314</v>
+      </c>
+      <c r="AI96" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="AJ96" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AK96" s="53">
+        <v>46314</v>
+      </c>
+      <c r="AL96" s="19" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="97" spans="1:38" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="C97" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D97" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>18</v>
+      </c>
       <c r="F97" s="6"/>
       <c r="G97" s="6"/>
-      <c r="H97" s="6"/>
-      <c r="I97" s="6"/>
+      <c r="H97" s="11" t="s">
+        <v>53</v>
+      </c>
       <c r="J97" s="6"/>
       <c r="K97" s="17"/>
       <c r="L97" s="17"/>
-      <c r="M97" s="17"/>
-    </row>
-    <row r="98" spans="1:13" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A98" s="51"/>
-      <c r="B98" s="8"/>
-      <c r="D98" s="12"/>
-      <c r="E98" s="6"/>
+      <c r="M97" s="26"/>
+      <c r="X97" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y97" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="Z97" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="AA97" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB97" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="AC97" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="AG97" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AH97" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="AI97" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="AJ97" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AK97" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="AL97" s="19" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="98" spans="1:38" ht="86.4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C98" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="D98" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>18</v>
+      </c>
       <c r="F98" s="6"/>
       <c r="G98" s="6"/>
-      <c r="H98" s="6"/>
+      <c r="H98" s="11" t="s">
+        <v>53</v>
+      </c>
       <c r="I98" s="6"/>
       <c r="J98" s="6"/>
-      <c r="K98" s="17"/>
-      <c r="L98" s="17"/>
-      <c r="M98" s="29">
-        <f>M3+M10+M33+M45+M50+M70+M82+M91</f>
+      <c r="K98" s="6"/>
+      <c r="L98" s="6"/>
+      <c r="M98" s="26"/>
+      <c r="P98">
+        <v>5</v>
+      </c>
+      <c r="S98" t="s">
+        <v>150</v>
+      </c>
+      <c r="X98" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA98" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB98" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="AC98" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="AG98" s="43" t="s">
+        <v>246</v>
+      </c>
+      <c r="AH98" s="19"/>
+      <c r="AI98" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="AJ98" s="43" t="s">
+        <v>246</v>
+      </c>
+      <c r="AK98" s="19"/>
+      <c r="AL98" s="19" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="99" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C99" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="D99" s="13"/>
+      <c r="E99" s="6"/>
+      <c r="F99" s="6"/>
+      <c r="G99" s="6"/>
+      <c r="H99" s="11"/>
+      <c r="I99" s="6"/>
+      <c r="J99" s="6"/>
+      <c r="K99" s="6"/>
+      <c r="L99" s="6"/>
+      <c r="M99" s="26"/>
+      <c r="X99" s="37"/>
+      <c r="AA99" s="46"/>
+      <c r="AG99" s="43"/>
+      <c r="AH99" s="19"/>
+      <c r="AI99" s="19"/>
+      <c r="AJ99" s="43"/>
+      <c r="AK99" s="19"/>
+      <c r="AL99" s="19"/>
+    </row>
+    <row r="100" spans="1:38" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A100" s="50" t="s">
+        <v>224</v>
+      </c>
+      <c r="B100" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C100" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="M100" s="28">
+        <v>156</v>
+      </c>
+      <c r="X100" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="AA100" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="AG100" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="AH100" s="19"/>
+      <c r="AI100" s="19"/>
+      <c r="AJ100" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="AK100" s="19"/>
+      <c r="AL100" s="19"/>
+    </row>
+    <row r="101" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B101" s="18"/>
+      <c r="C101" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D101" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="E101" s="6"/>
+      <c r="F101" s="6"/>
+      <c r="G101" s="6"/>
+      <c r="H101" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="J101" s="6"/>
+      <c r="K101" s="6"/>
+      <c r="L101" s="6"/>
+      <c r="M101" s="26"/>
+      <c r="X101" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA101" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AG101" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AH101" s="19"/>
+      <c r="AI101" s="19"/>
+      <c r="AJ101" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AK101" s="19"/>
+      <c r="AL101" s="19"/>
+    </row>
+    <row r="102" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B102" s="18"/>
+      <c r="C102" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="D102" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="E102" s="6"/>
+      <c r="F102" s="6"/>
+      <c r="G102" s="6"/>
+      <c r="H102" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="J102" s="6"/>
+      <c r="K102" s="6"/>
+      <c r="L102" s="6"/>
+      <c r="M102" s="26"/>
+      <c r="X102" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA102" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AG102" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AH102" s="19"/>
+      <c r="AI102" s="19"/>
+      <c r="AJ102" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AK102" s="19"/>
+      <c r="AL102" s="19"/>
+    </row>
+    <row r="103" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A103"/>
+      <c r="B103" s="18"/>
+      <c r="C103"/>
+      <c r="D103" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="E103" s="6"/>
+      <c r="F103" s="6"/>
+      <c r="G103" s="6"/>
+      <c r="H103" s="21"/>
+      <c r="J103" s="6"/>
+      <c r="K103" s="6"/>
+      <c r="L103" s="6"/>
+      <c r="M103" s="26"/>
+      <c r="AG103" s="19"/>
+      <c r="AH103" s="19"/>
+      <c r="AI103" s="19"/>
+      <c r="AJ103" s="19"/>
+      <c r="AK103" s="19"/>
+      <c r="AL103" s="19"/>
+    </row>
+    <row r="104" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A104"/>
+      <c r="B104" s="18"/>
+      <c r="C104"/>
+      <c r="D104" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="E104" s="6"/>
+      <c r="F104" s="6"/>
+      <c r="G104" s="6"/>
+      <c r="H104" s="21"/>
+      <c r="J104" s="6"/>
+      <c r="K104" s="6"/>
+      <c r="L104" s="6"/>
+      <c r="M104" s="26"/>
+      <c r="AG104" s="19"/>
+      <c r="AH104" s="19"/>
+      <c r="AI104" s="19"/>
+      <c r="AJ104" s="19"/>
+      <c r="AK104" s="19"/>
+      <c r="AL104" s="19"/>
+    </row>
+    <row r="105" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A105"/>
+      <c r="B105" s="18"/>
+      <c r="C105"/>
+      <c r="D105" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="E105" s="6"/>
+      <c r="F105" s="6"/>
+      <c r="G105" s="6"/>
+      <c r="H105" s="21"/>
+      <c r="J105" s="6"/>
+      <c r="K105" s="6"/>
+      <c r="L105" s="6"/>
+      <c r="M105" s="26"/>
+      <c r="AG105" s="19"/>
+      <c r="AH105" s="19"/>
+      <c r="AI105" s="19"/>
+      <c r="AJ105" s="19"/>
+      <c r="AK105" s="19"/>
+      <c r="AL105" s="19"/>
+    </row>
+    <row r="106" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A106"/>
+      <c r="B106" s="18"/>
+      <c r="C106"/>
+      <c r="D106" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E106" s="6"/>
+      <c r="F106" s="6"/>
+      <c r="G106" s="6"/>
+      <c r="H106" s="21"/>
+      <c r="J106" s="6"/>
+      <c r="K106" s="6"/>
+      <c r="L106" s="6"/>
+      <c r="M106" s="26"/>
+      <c r="AG106" s="19"/>
+      <c r="AH106" s="19"/>
+      <c r="AI106" s="19"/>
+      <c r="AJ106" s="19"/>
+      <c r="AK106" s="19"/>
+      <c r="AL106" s="19"/>
+    </row>
+    <row r="107" spans="1:38" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A107"/>
+      <c r="B107" s="18"/>
+      <c r="C107"/>
+      <c r="D107" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="E107" s="6"/>
+      <c r="F107" s="6"/>
+      <c r="G107" s="6"/>
+      <c r="H107" s="21"/>
+      <c r="J107" s="6"/>
+      <c r="K107" s="6"/>
+      <c r="L107" s="6"/>
+      <c r="M107" s="26"/>
+      <c r="AG107" s="19"/>
+      <c r="AH107" s="19"/>
+      <c r="AI107" s="19"/>
+      <c r="AJ107" s="19"/>
+      <c r="AK107" s="19"/>
+      <c r="AL107" s="19"/>
+    </row>
+    <row r="108" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B108" s="18"/>
+      <c r="C108" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D108" s="13"/>
+      <c r="E108" s="6"/>
+      <c r="F108" s="6"/>
+      <c r="G108" s="6"/>
+      <c r="H108" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="J108" s="6"/>
+      <c r="K108" s="6"/>
+      <c r="L108" s="6"/>
+      <c r="M108" s="26"/>
+      <c r="X108" s="42" t="s">
+        <v>202</v>
+      </c>
+      <c r="AA108" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AG108" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AH108" s="19"/>
+      <c r="AI108" s="19"/>
+      <c r="AJ108" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK108" s="19"/>
+      <c r="AL108" s="19"/>
+    </row>
+    <row r="109" spans="1:38" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A109" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="B109" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C109" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="M109" s="28">
+        <v>89</v>
+      </c>
+      <c r="X109" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="AA109" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="AG109" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="AH109" s="19"/>
+      <c r="AI109" s="19"/>
+      <c r="AJ109" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="AK109" s="19"/>
+      <c r="AL109" s="19"/>
+    </row>
+    <row r="110" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="48"/>
+      <c r="B110" s="18"/>
+      <c r="C110" s="16"/>
+      <c r="D110" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E110" s="6"/>
+      <c r="F110" s="6"/>
+      <c r="G110" s="6"/>
+      <c r="H110" s="21"/>
+      <c r="J110" s="6"/>
+      <c r="K110" s="6"/>
+      <c r="L110" s="6"/>
+      <c r="M110" s="26"/>
+    </row>
+    <row r="111" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="48"/>
+      <c r="B111" s="18"/>
+      <c r="C111" s="16"/>
+      <c r="D111" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="E111" s="6"/>
+      <c r="F111" s="6"/>
+      <c r="G111" s="6"/>
+      <c r="H111" s="21"/>
+      <c r="J111" s="6"/>
+      <c r="K111" s="6"/>
+      <c r="L111" s="6"/>
+      <c r="M111" s="26"/>
+    </row>
+    <row r="112" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="48"/>
+      <c r="B112" s="18"/>
+      <c r="C112" s="16"/>
+      <c r="D112" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="E112" s="6"/>
+      <c r="F112" s="6"/>
+      <c r="G112" s="6"/>
+      <c r="H112" s="21"/>
+      <c r="J112" s="6"/>
+      <c r="K112" s="6"/>
+      <c r="L112" s="6"/>
+      <c r="M112" s="26"/>
+    </row>
+    <row r="113" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="48"/>
+      <c r="B113" s="18"/>
+      <c r="C113" s="16"/>
+      <c r="D113" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="E113" s="6"/>
+      <c r="F113" s="6"/>
+      <c r="G113" s="6"/>
+      <c r="H113" s="21"/>
+      <c r="J113" s="6"/>
+      <c r="K113" s="6"/>
+      <c r="L113" s="6"/>
+      <c r="M113" s="26"/>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A114" s="48"/>
+      <c r="B114" s="18"/>
+      <c r="C114" s="18"/>
+      <c r="D114" s="18"/>
+      <c r="E114" s="18"/>
+      <c r="F114" s="18"/>
+      <c r="G114" s="18"/>
+      <c r="H114" s="18"/>
+      <c r="I114" s="19"/>
+      <c r="J114" s="12"/>
+      <c r="K114" s="17"/>
+      <c r="L114" s="17"/>
+      <c r="M114" s="17"/>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D115" s="12"/>
+      <c r="E115" s="6"/>
+      <c r="F115" s="6"/>
+      <c r="G115" s="6"/>
+      <c r="H115" s="6"/>
+      <c r="I115" s="6"/>
+      <c r="J115" s="6"/>
+      <c r="K115" s="17"/>
+      <c r="L115" s="17"/>
+      <c r="M115" s="17"/>
+    </row>
+    <row r="116" spans="1:13" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A116" s="51"/>
+      <c r="B116" s="8"/>
+      <c r="D116" s="12"/>
+      <c r="E116" s="6"/>
+      <c r="F116" s="6"/>
+      <c r="G116" s="6"/>
+      <c r="H116" s="6"/>
+      <c r="I116" s="6"/>
+      <c r="J116" s="6"/>
+      <c r="K116" s="17"/>
+      <c r="L116" s="17"/>
+      <c r="M116" s="29">
+        <f>M3+M10+M33+M45+M58+M86+M100+M109</f>
         <v>825</v>
       </c>
     </row>
-    <row r="103" spans="1:13" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A103" s="52" t="s">
+    <row r="121" spans="1:13" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A121" s="52" t="s">
+        <v>130</v>
+      </c>
+      <c r="B121" s="1"/>
+    </row>
+    <row r="122" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A122" s="52" t="s">
         <v>131</v>
       </c>
-      <c r="B103" s="1"/>
-    </row>
-    <row r="104" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A104" s="52" t="s">
+      <c r="B122" s="1"/>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A124" s="51" t="s">
         <v>132</v>
       </c>
-      <c r="B104" s="1"/>
-    </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A106" s="51" t="s">
+      <c r="B124" s="8"/>
+      <c r="C124" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="B106" s="8"/>
-      <c r="C106" s="15" t="s">
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A125" s="51" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A107" s="51" t="s">
+      <c r="B125" s="8"/>
+      <c r="C125" s="15" t="s">
         <v>135</v>
-      </c>
-      <c r="B107" s="8"/>
-      <c r="C107" s="15" t="s">
-        <v>136</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D71" r:id="rId1" xr:uid="{DA624192-AF92-421C-B882-954902949584}"/>
+    <hyperlink ref="D87" r:id="rId1" xr:uid="{DA624192-AF92-421C-B882-954902949584}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
@@ -4373,15 +5840,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Estado xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">En curso</Estado>
@@ -4416,7 +5874,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010021AB849DB9524648A8F6CDAE5A42EE85" ma:contentTypeVersion="54" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5cf342e325584cfc73779b32cd8516cb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xmlns:ns3="06fec347-a373-485e-bb4f-f611040a1dd3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="97bec9e280156beb57af844d85b9963b" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -4816,15 +6274,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5D2ED08-240E-422E-815D-BA2AE63D0B29}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C64067D8-2529-40F8-873F-7DCFF29E6C0A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -4842,7 +6301,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B271E1E9-4B5A-43C8-93E9-EF9A1A456C27}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4860,4 +6319,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5D2ED08-240E-422E-815D-BA2AE63D0B29}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>